--- a/output/version3/test/15-5/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>733</v>
+        <v>564</v>
       </c>
       <c r="C2" t="n">
-        <v>709</v>
+        <v>625</v>
       </c>
       <c r="D2" t="n">
-        <v>732</v>
+        <v>614</v>
       </c>
       <c r="E2" t="n">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>762</v>
+        <v>593</v>
       </c>
       <c r="G2" t="n">
-        <v>725</v>
+        <v>601</v>
       </c>
       <c r="H2" t="n">
-        <v>698</v>
+        <v>671</v>
       </c>
       <c r="I2" t="n">
-        <v>795</v>
+        <v>601</v>
       </c>
       <c r="J2" t="n">
-        <v>712</v>
+        <v>601</v>
       </c>
       <c r="K2" t="n">
-        <v>642</v>
+        <v>595</v>
       </c>
       <c r="L2" t="n">
-        <v>723.5</v>
+        <v>620.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>804</v>
+        <v>846</v>
       </c>
       <c r="C3" t="n">
-        <v>1048</v>
+        <v>820</v>
       </c>
       <c r="D3" t="n">
-        <v>1014</v>
+        <v>661</v>
       </c>
       <c r="E3" t="n">
-        <v>934</v>
+        <v>798</v>
       </c>
       <c r="F3" t="n">
-        <v>910</v>
+        <v>852</v>
       </c>
       <c r="G3" t="n">
-        <v>862</v>
+        <v>755</v>
       </c>
       <c r="H3" t="n">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="I3" t="n">
-        <v>948</v>
+        <v>805</v>
       </c>
       <c r="J3" t="n">
-        <v>909</v>
+        <v>701</v>
       </c>
       <c r="K3" t="n">
-        <v>1001</v>
+        <v>813</v>
       </c>
       <c r="L3" t="n">
-        <v>926.1</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>771</v>
+        <v>851</v>
       </c>
       <c r="C4" t="n">
-        <v>818</v>
+        <v>738</v>
       </c>
       <c r="D4" t="n">
-        <v>966</v>
+        <v>822</v>
       </c>
       <c r="E4" t="n">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="F4" t="n">
-        <v>932</v>
+        <v>790</v>
       </c>
       <c r="G4" t="n">
-        <v>890</v>
+        <v>713</v>
       </c>
       <c r="H4" t="n">
-        <v>846</v>
+        <v>816</v>
       </c>
       <c r="I4" t="n">
-        <v>809</v>
+        <v>848</v>
       </c>
       <c r="J4" t="n">
-        <v>874</v>
+        <v>825</v>
       </c>
       <c r="K4" t="n">
-        <v>899</v>
+        <v>764</v>
       </c>
       <c r="L4" t="n">
-        <v>870.1</v>
+        <v>805.6</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1070</v>
+        <v>956</v>
       </c>
       <c r="C5" t="n">
-        <v>953</v>
+        <v>819</v>
       </c>
       <c r="D5" t="n">
-        <v>1004</v>
+        <v>921</v>
       </c>
       <c r="E5" t="n">
-        <v>968</v>
+        <v>840</v>
       </c>
       <c r="F5" t="n">
-        <v>1085</v>
+        <v>787</v>
       </c>
       <c r="G5" t="n">
-        <v>941</v>
+        <v>862</v>
       </c>
       <c r="H5" t="n">
-        <v>980</v>
+        <v>991</v>
       </c>
       <c r="I5" t="n">
-        <v>1170</v>
+        <v>959</v>
       </c>
       <c r="J5" t="n">
-        <v>990</v>
+        <v>828</v>
       </c>
       <c r="K5" t="n">
-        <v>1026</v>
+        <v>927</v>
       </c>
       <c r="L5" t="n">
-        <v>1018.7</v>
+        <v>889</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="C6" t="n">
-        <v>709</v>
+        <v>576</v>
       </c>
       <c r="D6" t="n">
-        <v>767</v>
+        <v>671</v>
       </c>
       <c r="E6" t="n">
-        <v>676</v>
+        <v>574</v>
       </c>
       <c r="F6" t="n">
-        <v>639</v>
+        <v>603</v>
       </c>
       <c r="G6" t="n">
-        <v>700</v>
+        <v>628</v>
       </c>
       <c r="H6" t="n">
-        <v>703</v>
+        <v>666</v>
       </c>
       <c r="I6" t="n">
-        <v>786</v>
+        <v>646</v>
       </c>
       <c r="J6" t="n">
-        <v>735</v>
+        <v>583</v>
       </c>
       <c r="K6" t="n">
-        <v>619</v>
+        <v>743</v>
       </c>
       <c r="L6" t="n">
-        <v>704.9</v>
+        <v>641.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>969</v>
+        <v>836</v>
       </c>
       <c r="C7" t="n">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="D7" t="n">
-        <v>1015</v>
+        <v>811</v>
       </c>
       <c r="E7" t="n">
-        <v>975</v>
+        <v>935</v>
       </c>
       <c r="F7" t="n">
-        <v>1056</v>
+        <v>831</v>
       </c>
       <c r="G7" t="n">
-        <v>829</v>
+        <v>896</v>
       </c>
       <c r="H7" t="n">
-        <v>868</v>
+        <v>850</v>
       </c>
       <c r="I7" t="n">
-        <v>871</v>
+        <v>795</v>
       </c>
       <c r="J7" t="n">
-        <v>1006</v>
+        <v>777</v>
       </c>
       <c r="K7" t="n">
-        <v>995</v>
+        <v>856</v>
       </c>
       <c r="L7" t="n">
-        <v>952.8</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>741</v>
+        <v>700</v>
       </c>
       <c r="C8" t="n">
-        <v>758</v>
+        <v>715</v>
       </c>
       <c r="D8" t="n">
-        <v>742</v>
+        <v>698</v>
       </c>
       <c r="E8" t="n">
-        <v>763</v>
+        <v>857</v>
       </c>
       <c r="F8" t="n">
-        <v>698</v>
+        <v>652</v>
       </c>
       <c r="G8" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="I8" t="n">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="J8" t="n">
-        <v>829</v>
+        <v>773</v>
       </c>
       <c r="K8" t="n">
-        <v>794</v>
+        <v>707</v>
       </c>
       <c r="L8" t="n">
-        <v>757.3</v>
+        <v>722.3</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
+        <v>639</v>
+      </c>
+      <c r="C9" t="n">
         <v>680</v>
       </c>
-      <c r="C9" t="n">
-        <v>781</v>
-      </c>
       <c r="D9" t="n">
-        <v>735</v>
+        <v>683</v>
       </c>
       <c r="E9" t="n">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="F9" t="n">
-        <v>782</v>
+        <v>709</v>
       </c>
       <c r="G9" t="n">
-        <v>789</v>
+        <v>588</v>
       </c>
       <c r="H9" t="n">
-        <v>746</v>
+        <v>612</v>
       </c>
       <c r="I9" t="n">
-        <v>723</v>
+        <v>690</v>
       </c>
       <c r="J9" t="n">
-        <v>737</v>
+        <v>614</v>
       </c>
       <c r="K9" t="n">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="L9" t="n">
-        <v>725.1</v>
+        <v>654.3</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>919</v>
+        <v>780</v>
       </c>
       <c r="C10" t="n">
-        <v>992</v>
+        <v>832</v>
       </c>
       <c r="D10" t="n">
-        <v>1002</v>
+        <v>768</v>
       </c>
       <c r="E10" t="n">
-        <v>916</v>
+        <v>865</v>
       </c>
       <c r="F10" t="n">
-        <v>898</v>
+        <v>824</v>
       </c>
       <c r="G10" t="n">
-        <v>914</v>
+        <v>865</v>
       </c>
       <c r="H10" t="n">
-        <v>995</v>
+        <v>920</v>
       </c>
       <c r="I10" t="n">
-        <v>915</v>
+        <v>790</v>
       </c>
       <c r="J10" t="n">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="K10" t="n">
-        <v>856</v>
+        <v>776</v>
       </c>
       <c r="L10" t="n">
-        <v>924.4</v>
+        <v>824.1</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>831</v>
+        <v>752</v>
       </c>
       <c r="C11" t="n">
-        <v>961</v>
+        <v>751</v>
       </c>
       <c r="D11" t="n">
-        <v>785</v>
+        <v>750</v>
       </c>
       <c r="E11" t="n">
-        <v>913</v>
+        <v>799</v>
       </c>
       <c r="F11" t="n">
-        <v>1047</v>
+        <v>693</v>
       </c>
       <c r="G11" t="n">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="H11" t="n">
-        <v>837</v>
+        <v>708</v>
       </c>
       <c r="I11" t="n">
-        <v>817</v>
+        <v>734</v>
       </c>
       <c r="J11" t="n">
-        <v>984</v>
+        <v>738</v>
       </c>
       <c r="K11" t="n">
-        <v>948</v>
+        <v>819</v>
       </c>
       <c r="L11" t="n">
-        <v>898.8</v>
+        <v>760.6</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>821</v>
+        <v>765</v>
       </c>
       <c r="C12" t="n">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="D12" t="n">
-        <v>777</v>
+        <v>692</v>
       </c>
       <c r="E12" t="n">
-        <v>761</v>
+        <v>810</v>
       </c>
       <c r="F12" t="n">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G12" t="n">
-        <v>643</v>
+        <v>725</v>
       </c>
       <c r="H12" t="n">
-        <v>687</v>
+        <v>722</v>
       </c>
       <c r="I12" t="n">
-        <v>807</v>
+        <v>701</v>
       </c>
       <c r="J12" t="n">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="K12" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L12" t="n">
-        <v>748.7</v>
+        <v>742.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>763</v>
+        <v>584</v>
       </c>
       <c r="C13" t="n">
-        <v>705</v>
+        <v>644</v>
       </c>
       <c r="D13" t="n">
-        <v>784</v>
+        <v>742</v>
       </c>
       <c r="E13" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F13" t="n">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="G13" t="n">
-        <v>623</v>
+        <v>700</v>
       </c>
       <c r="H13" t="n">
-        <v>835</v>
+        <v>621</v>
       </c>
       <c r="I13" t="n">
-        <v>693</v>
+        <v>733</v>
       </c>
       <c r="J13" t="n">
-        <v>728</v>
+        <v>671</v>
       </c>
       <c r="K13" t="n">
-        <v>707</v>
+        <v>663</v>
       </c>
       <c r="L13" t="n">
-        <v>722</v>
+        <v>673.3</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>730</v>
+        <v>664</v>
       </c>
       <c r="C14" t="n">
-        <v>803</v>
+        <v>607</v>
       </c>
       <c r="D14" t="n">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="E14" t="n">
-        <v>639</v>
+        <v>681</v>
       </c>
       <c r="F14" t="n">
-        <v>799</v>
+        <v>667</v>
       </c>
       <c r="G14" t="n">
-        <v>863</v>
+        <v>652</v>
       </c>
       <c r="H14" t="n">
-        <v>733</v>
+        <v>646</v>
       </c>
       <c r="I14" t="n">
-        <v>756</v>
+        <v>591</v>
       </c>
       <c r="J14" t="n">
-        <v>763</v>
+        <v>700</v>
       </c>
       <c r="K14" t="n">
-        <v>703</v>
+        <v>565</v>
       </c>
       <c r="L14" t="n">
-        <v>748.6</v>
+        <v>645.2</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>978</v>
+        <v>857</v>
       </c>
       <c r="C15" t="n">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D15" t="n">
-        <v>833</v>
+        <v>739</v>
       </c>
       <c r="E15" t="n">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="F15" t="n">
-        <v>867</v>
+        <v>753</v>
       </c>
       <c r="G15" t="n">
-        <v>891</v>
+        <v>750</v>
       </c>
       <c r="H15" t="n">
-        <v>851</v>
+        <v>806</v>
       </c>
       <c r="I15" t="n">
-        <v>968</v>
+        <v>767</v>
       </c>
       <c r="J15" t="n">
-        <v>878</v>
+        <v>798</v>
       </c>
       <c r="K15" t="n">
-        <v>827</v>
+        <v>761</v>
       </c>
       <c r="L15" t="n">
-        <v>877.1</v>
+        <v>791.7</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>784</v>
+        <v>757</v>
       </c>
       <c r="C16" t="n">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D16" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="E16" t="n">
-        <v>894</v>
+        <v>763</v>
       </c>
       <c r="F16" t="n">
-        <v>861</v>
+        <v>738</v>
       </c>
       <c r="G16" t="n">
-        <v>801</v>
+        <v>725</v>
       </c>
       <c r="H16" t="n">
-        <v>901</v>
+        <v>761</v>
       </c>
       <c r="I16" t="n">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="J16" t="n">
-        <v>852</v>
+        <v>762</v>
       </c>
       <c r="K16" t="n">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="L16" t="n">
-        <v>823.8</v>
+        <v>759.6</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="C17" t="n">
-        <v>933</v>
+        <v>840</v>
       </c>
       <c r="D17" t="n">
-        <v>832</v>
+        <v>736</v>
       </c>
       <c r="E17" t="n">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="F17" t="n">
-        <v>959</v>
+        <v>902</v>
       </c>
       <c r="G17" t="n">
-        <v>915</v>
+        <v>798</v>
       </c>
       <c r="H17" t="n">
-        <v>783</v>
+        <v>801</v>
       </c>
       <c r="I17" t="n">
-        <v>824</v>
+        <v>849</v>
       </c>
       <c r="J17" t="n">
-        <v>861</v>
+        <v>745</v>
       </c>
       <c r="K17" t="n">
-        <v>973</v>
+        <v>855</v>
       </c>
       <c r="L17" t="n">
-        <v>874.5</v>
+        <v>823.8</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>712</v>
+        <v>739</v>
       </c>
       <c r="C18" t="n">
-        <v>790</v>
+        <v>727</v>
       </c>
       <c r="D18" t="n">
-        <v>770</v>
+        <v>659</v>
       </c>
       <c r="E18" t="n">
-        <v>754</v>
+        <v>720</v>
       </c>
       <c r="F18" t="n">
-        <v>750</v>
+        <v>687</v>
       </c>
       <c r="G18" t="n">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="H18" t="n">
-        <v>717</v>
+        <v>672</v>
       </c>
       <c r="I18" t="n">
-        <v>758</v>
+        <v>719</v>
       </c>
       <c r="J18" t="n">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="K18" t="n">
-        <v>683</v>
+        <v>803</v>
       </c>
       <c r="L18" t="n">
-        <v>734.9</v>
+        <v>710.8</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>774</v>
+        <v>848</v>
       </c>
       <c r="C19" t="n">
-        <v>835</v>
+        <v>742</v>
       </c>
       <c r="D19" t="n">
-        <v>820</v>
+        <v>693</v>
       </c>
       <c r="E19" t="n">
-        <v>807</v>
+        <v>679</v>
       </c>
       <c r="F19" t="n">
-        <v>758</v>
+        <v>685</v>
       </c>
       <c r="G19" t="n">
-        <v>846</v>
+        <v>787</v>
       </c>
       <c r="H19" t="n">
-        <v>759</v>
+        <v>700</v>
       </c>
       <c r="I19" t="n">
-        <v>774</v>
+        <v>656</v>
       </c>
       <c r="J19" t="n">
-        <v>715</v>
+        <v>788</v>
       </c>
       <c r="K19" t="n">
-        <v>717</v>
+        <v>781</v>
       </c>
       <c r="L19" t="n">
-        <v>780.5</v>
+        <v>735.9</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>778</v>
+        <v>645</v>
       </c>
       <c r="C20" t="n">
-        <v>833</v>
+        <v>756</v>
       </c>
       <c r="D20" t="n">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="E20" t="n">
-        <v>783</v>
+        <v>763</v>
       </c>
       <c r="F20" t="n">
-        <v>835</v>
+        <v>633</v>
       </c>
       <c r="G20" t="n">
-        <v>749</v>
+        <v>875</v>
       </c>
       <c r="H20" t="n">
-        <v>1119</v>
+        <v>788</v>
       </c>
       <c r="I20" t="n">
-        <v>943</v>
+        <v>765</v>
       </c>
       <c r="J20" t="n">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K20" t="n">
-        <v>975</v>
+        <v>779</v>
       </c>
       <c r="L20" t="n">
-        <v>858.1</v>
+        <v>755.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>805</v>
+        <v>743</v>
       </c>
       <c r="C21" t="n">
-        <v>823</v>
+        <v>725</v>
       </c>
       <c r="D21" t="n">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="E21" t="n">
-        <v>895</v>
+        <v>697</v>
       </c>
       <c r="F21" t="n">
-        <v>748</v>
+        <v>713</v>
       </c>
       <c r="G21" t="n">
-        <v>722</v>
+        <v>797</v>
       </c>
       <c r="H21" t="n">
-        <v>783</v>
+        <v>688</v>
       </c>
       <c r="I21" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="J21" t="n">
-        <v>749</v>
+        <v>772</v>
       </c>
       <c r="K21" t="n">
-        <v>787</v>
+        <v>765</v>
       </c>
       <c r="L21" t="n">
-        <v>784.4</v>
+        <v>741.1</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
+        <v>766</v>
+      </c>
+      <c r="C22" t="n">
+        <v>571</v>
+      </c>
+      <c r="D22" t="n">
+        <v>585</v>
+      </c>
+      <c r="E22" t="n">
+        <v>645</v>
+      </c>
+      <c r="F22" t="n">
         <v>599</v>
       </c>
-      <c r="C22" t="n">
-        <v>745</v>
-      </c>
-      <c r="D22" t="n">
-        <v>705</v>
-      </c>
-      <c r="E22" t="n">
-        <v>586</v>
-      </c>
-      <c r="F22" t="n">
-        <v>653</v>
-      </c>
       <c r="G22" t="n">
-        <v>714</v>
+        <v>626</v>
       </c>
       <c r="H22" t="n">
-        <v>707</v>
+        <v>674</v>
       </c>
       <c r="I22" t="n">
-        <v>733</v>
+        <v>624</v>
       </c>
       <c r="J22" t="n">
-        <v>892</v>
+        <v>635</v>
       </c>
       <c r="K22" t="n">
-        <v>812</v>
+        <v>630</v>
       </c>
       <c r="L22" t="n">
-        <v>714.6</v>
+        <v>635.5</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>973</v>
+        <v>665</v>
       </c>
       <c r="C23" t="n">
-        <v>845</v>
+        <v>726</v>
       </c>
       <c r="D23" t="n">
-        <v>793</v>
+        <v>776</v>
       </c>
       <c r="E23" t="n">
-        <v>837</v>
+        <v>680</v>
       </c>
       <c r="F23" t="n">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="G23" t="n">
-        <v>800</v>
+        <v>757</v>
       </c>
       <c r="H23" t="n">
-        <v>867</v>
+        <v>903</v>
       </c>
       <c r="I23" t="n">
-        <v>960</v>
+        <v>805</v>
       </c>
       <c r="J23" t="n">
-        <v>768</v>
+        <v>688</v>
       </c>
       <c r="K23" t="n">
-        <v>705</v>
+        <v>728</v>
       </c>
       <c r="L23" t="n">
-        <v>835.5</v>
+        <v>752.7</v>
       </c>
     </row>
     <row r="24">
@@ -1310,34 +1310,34 @@
         <v>756</v>
       </c>
       <c r="C24" t="n">
-        <v>942</v>
+        <v>730</v>
       </c>
       <c r="D24" t="n">
-        <v>741</v>
+        <v>826</v>
       </c>
       <c r="E24" t="n">
-        <v>919</v>
+        <v>784</v>
       </c>
       <c r="F24" t="n">
-        <v>896</v>
+        <v>734</v>
       </c>
       <c r="G24" t="n">
-        <v>680</v>
+        <v>760</v>
       </c>
       <c r="H24" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I24" t="n">
-        <v>771</v>
+        <v>870</v>
       </c>
       <c r="J24" t="n">
-        <v>905</v>
+        <v>798</v>
       </c>
       <c r="K24" t="n">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="L24" t="n">
-        <v>816.7</v>
+        <v>780.4</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>622</v>
+        <v>597</v>
       </c>
       <c r="C25" t="n">
-        <v>747</v>
+        <v>709</v>
       </c>
       <c r="D25" t="n">
-        <v>769</v>
+        <v>716</v>
       </c>
       <c r="E25" t="n">
-        <v>737</v>
+        <v>683</v>
       </c>
       <c r="F25" t="n">
-        <v>662</v>
+        <v>763</v>
       </c>
       <c r="G25" t="n">
-        <v>787</v>
+        <v>765</v>
       </c>
       <c r="H25" t="n">
-        <v>697</v>
+        <v>772</v>
       </c>
       <c r="I25" t="n">
-        <v>757</v>
+        <v>701</v>
       </c>
       <c r="J25" t="n">
-        <v>823</v>
+        <v>690</v>
       </c>
       <c r="K25" t="n">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="L25" t="n">
-        <v>736</v>
+        <v>715.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="C26" t="n">
-        <v>871</v>
+        <v>717</v>
       </c>
       <c r="D26" t="n">
-        <v>983</v>
+        <v>842</v>
       </c>
       <c r="E26" t="n">
-        <v>809</v>
+        <v>741</v>
       </c>
       <c r="F26" t="n">
-        <v>775</v>
+        <v>849</v>
       </c>
       <c r="G26" t="n">
-        <v>850</v>
+        <v>791</v>
       </c>
       <c r="H26" t="n">
-        <v>851</v>
+        <v>714</v>
       </c>
       <c r="I26" t="n">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="J26" t="n">
-        <v>908</v>
+        <v>821</v>
       </c>
       <c r="K26" t="n">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="L26" t="n">
-        <v>847.2</v>
+        <v>792</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>913</v>
+        <v>752</v>
       </c>
       <c r="C27" t="n">
-        <v>830</v>
+        <v>945</v>
       </c>
       <c r="D27" t="n">
-        <v>965</v>
+        <v>788</v>
       </c>
       <c r="E27" t="n">
-        <v>972</v>
+        <v>877</v>
       </c>
       <c r="F27" t="n">
-        <v>914</v>
+        <v>868</v>
       </c>
       <c r="G27" t="n">
-        <v>952</v>
+        <v>768</v>
       </c>
       <c r="H27" t="n">
-        <v>1091</v>
+        <v>797</v>
       </c>
       <c r="I27" t="n">
-        <v>881</v>
+        <v>760</v>
       </c>
       <c r="J27" t="n">
-        <v>935</v>
+        <v>792</v>
       </c>
       <c r="K27" t="n">
-        <v>983</v>
+        <v>730</v>
       </c>
       <c r="L27" t="n">
-        <v>943.6</v>
+        <v>807.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>849</v>
+        <v>677</v>
       </c>
       <c r="C28" t="n">
-        <v>752</v>
+        <v>676</v>
       </c>
       <c r="D28" t="n">
-        <v>792</v>
+        <v>703</v>
       </c>
       <c r="E28" t="n">
-        <v>823</v>
+        <v>753</v>
       </c>
       <c r="F28" t="n">
-        <v>835</v>
+        <v>740</v>
       </c>
       <c r="G28" t="n">
-        <v>781</v>
+        <v>665</v>
       </c>
       <c r="H28" t="n">
-        <v>691</v>
+        <v>622</v>
       </c>
       <c r="I28" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J28" t="n">
-        <v>810</v>
+        <v>693</v>
       </c>
       <c r="K28" t="n">
-        <v>744</v>
+        <v>657</v>
       </c>
       <c r="L28" t="n">
-        <v>775.2</v>
+        <v>686.3</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C29" t="n">
-        <v>784</v>
+        <v>744</v>
       </c>
       <c r="D29" t="n">
-        <v>795</v>
+        <v>727</v>
       </c>
       <c r="E29" t="n">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F29" t="n">
-        <v>773</v>
+        <v>756</v>
       </c>
       <c r="G29" t="n">
-        <v>812</v>
+        <v>699</v>
       </c>
       <c r="H29" t="n">
-        <v>810</v>
+        <v>675</v>
       </c>
       <c r="I29" t="n">
-        <v>891</v>
+        <v>832</v>
       </c>
       <c r="J29" t="n">
-        <v>894</v>
+        <v>797</v>
       </c>
       <c r="K29" t="n">
-        <v>783</v>
+        <v>936</v>
       </c>
       <c r="L29" t="n">
-        <v>794.4</v>
+        <v>755.4</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>923</v>
+        <v>750</v>
       </c>
       <c r="C30" t="n">
-        <v>908</v>
+        <v>618</v>
       </c>
       <c r="D30" t="n">
-        <v>818</v>
+        <v>755</v>
       </c>
       <c r="E30" t="n">
-        <v>897</v>
+        <v>650</v>
       </c>
       <c r="F30" t="n">
+        <v>846</v>
+      </c>
+      <c r="G30" t="n">
+        <v>662</v>
+      </c>
+      <c r="H30" t="n">
         <v>876</v>
       </c>
-      <c r="G30" t="n">
-        <v>926</v>
-      </c>
-      <c r="H30" t="n">
-        <v>908</v>
-      </c>
       <c r="I30" t="n">
-        <v>895</v>
+        <v>681</v>
       </c>
       <c r="J30" t="n">
-        <v>772</v>
+        <v>882</v>
       </c>
       <c r="K30" t="n">
-        <v>988</v>
+        <v>704</v>
       </c>
       <c r="L30" t="n">
-        <v>891.1</v>
+        <v>742.4</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>746</v>
+        <v>683</v>
       </c>
       <c r="C31" t="n">
-        <v>801</v>
+        <v>769</v>
       </c>
       <c r="D31" t="n">
-        <v>805</v>
+        <v>652</v>
       </c>
       <c r="E31" t="n">
-        <v>715</v>
+        <v>698</v>
       </c>
       <c r="F31" t="n">
-        <v>805</v>
+        <v>755</v>
       </c>
       <c r="G31" t="n">
-        <v>713</v>
+        <v>643</v>
       </c>
       <c r="H31" t="n">
-        <v>735</v>
+        <v>814</v>
       </c>
       <c r="I31" t="n">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="J31" t="n">
-        <v>667</v>
+        <v>690</v>
       </c>
       <c r="K31" t="n">
-        <v>802</v>
+        <v>849</v>
       </c>
       <c r="L31" t="n">
-        <v>752</v>
+        <v>727.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>758</v>
+        <v>673</v>
       </c>
       <c r="C32" t="n">
-        <v>691</v>
+        <v>583</v>
       </c>
       <c r="D32" t="n">
-        <v>828</v>
+        <v>538</v>
       </c>
       <c r="E32" t="n">
-        <v>899</v>
+        <v>682</v>
       </c>
       <c r="F32" t="n">
-        <v>710</v>
+        <v>643</v>
       </c>
       <c r="G32" t="n">
-        <v>678</v>
+        <v>748</v>
       </c>
       <c r="H32" t="n">
-        <v>774</v>
+        <v>725</v>
       </c>
       <c r="I32" t="n">
-        <v>819</v>
+        <v>700</v>
       </c>
       <c r="J32" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="K32" t="n">
-        <v>656</v>
+        <v>781</v>
       </c>
       <c r="L32" t="n">
-        <v>745.4</v>
+        <v>671.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>804</v>
+        <v>731</v>
       </c>
       <c r="C33" t="n">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="D33" t="n">
-        <v>839</v>
+        <v>750</v>
       </c>
       <c r="E33" t="n">
-        <v>908</v>
+        <v>732</v>
       </c>
       <c r="F33" t="n">
-        <v>762</v>
+        <v>720</v>
       </c>
       <c r="G33" t="n">
-        <v>852</v>
+        <v>773</v>
       </c>
       <c r="H33" t="n">
-        <v>813</v>
+        <v>747</v>
       </c>
       <c r="I33" t="n">
-        <v>929</v>
+        <v>784</v>
       </c>
       <c r="J33" t="n">
-        <v>798</v>
+        <v>697</v>
       </c>
       <c r="K33" t="n">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="L33" t="n">
-        <v>838</v>
+        <v>763.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>742</v>
+        <v>638</v>
       </c>
       <c r="C34" t="n">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="D34" t="n">
-        <v>801</v>
+        <v>730</v>
       </c>
       <c r="E34" t="n">
-        <v>798</v>
+        <v>689</v>
       </c>
       <c r="F34" t="n">
-        <v>836</v>
+        <v>663</v>
       </c>
       <c r="G34" t="n">
-        <v>694</v>
+        <v>722</v>
       </c>
       <c r="H34" t="n">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="I34" t="n">
-        <v>808</v>
+        <v>765</v>
       </c>
       <c r="J34" t="n">
-        <v>630</v>
+        <v>698</v>
       </c>
       <c r="K34" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="L34" t="n">
-        <v>745.3</v>
+        <v>703.2</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1015</v>
+        <v>829</v>
       </c>
       <c r="C35" t="n">
-        <v>1059</v>
+        <v>910</v>
       </c>
       <c r="D35" t="n">
-        <v>973</v>
+        <v>871</v>
       </c>
       <c r="E35" t="n">
-        <v>890</v>
+        <v>818</v>
       </c>
       <c r="F35" t="n">
-        <v>1027</v>
+        <v>871</v>
       </c>
       <c r="G35" t="n">
-        <v>854</v>
+        <v>812</v>
       </c>
       <c r="H35" t="n">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="I35" t="n">
-        <v>807</v>
+        <v>675</v>
       </c>
       <c r="J35" t="n">
-        <v>954</v>
+        <v>845</v>
       </c>
       <c r="K35" t="n">
-        <v>949</v>
+        <v>693</v>
       </c>
       <c r="L35" t="n">
-        <v>943.6</v>
+        <v>824.4</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="C36" t="n">
-        <v>730</v>
+        <v>654</v>
       </c>
       <c r="D36" t="n">
-        <v>701</v>
+        <v>606</v>
       </c>
       <c r="E36" t="n">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="F36" t="n">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="G36" t="n">
-        <v>642</v>
+        <v>582</v>
       </c>
       <c r="H36" t="n">
-        <v>729</v>
+        <v>623</v>
       </c>
       <c r="I36" t="n">
-        <v>688</v>
+        <v>629</v>
       </c>
       <c r="J36" t="n">
-        <v>668</v>
+        <v>592</v>
       </c>
       <c r="K36" t="n">
-        <v>689</v>
+        <v>733</v>
       </c>
       <c r="L36" t="n">
-        <v>677.6</v>
+        <v>634.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>787</v>
+        <v>741</v>
       </c>
       <c r="C37" t="n">
-        <v>849</v>
+        <v>720</v>
       </c>
       <c r="D37" t="n">
-        <v>802</v>
+        <v>774</v>
       </c>
       <c r="E37" t="n">
-        <v>878</v>
+        <v>733</v>
       </c>
       <c r="F37" t="n">
-        <v>796</v>
+        <v>762</v>
       </c>
       <c r="G37" t="n">
-        <v>759</v>
+        <v>835</v>
       </c>
       <c r="H37" t="n">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="I37" t="n">
-        <v>914</v>
+        <v>839</v>
       </c>
       <c r="J37" t="n">
-        <v>900</v>
+        <v>745</v>
       </c>
       <c r="K37" t="n">
-        <v>913</v>
+        <v>649</v>
       </c>
       <c r="L37" t="n">
-        <v>841.5</v>
+        <v>759.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>862</v>
+        <v>679</v>
       </c>
       <c r="C38" t="n">
-        <v>735</v>
+        <v>699</v>
       </c>
       <c r="D38" t="n">
-        <v>777</v>
+        <v>718</v>
       </c>
       <c r="E38" t="n">
-        <v>823</v>
+        <v>744</v>
       </c>
       <c r="F38" t="n">
-        <v>907</v>
+        <v>805</v>
       </c>
       <c r="G38" t="n">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="H38" t="n">
-        <v>813</v>
+        <v>707</v>
       </c>
       <c r="I38" t="n">
-        <v>890</v>
+        <v>821</v>
       </c>
       <c r="J38" t="n">
-        <v>836</v>
+        <v>789</v>
       </c>
       <c r="K38" t="n">
-        <v>896</v>
+        <v>871</v>
       </c>
       <c r="L38" t="n">
-        <v>832.7</v>
+        <v>757.5</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>806</v>
+        <v>687</v>
       </c>
       <c r="C39" t="n">
-        <v>741</v>
+        <v>584</v>
       </c>
       <c r="D39" t="n">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="E39" t="n">
-        <v>770</v>
+        <v>622</v>
       </c>
       <c r="F39" t="n">
-        <v>768</v>
+        <v>720</v>
       </c>
       <c r="G39" t="n">
-        <v>642</v>
+        <v>617</v>
       </c>
       <c r="H39" t="n">
-        <v>730</v>
+        <v>623</v>
       </c>
       <c r="I39" t="n">
-        <v>819</v>
+        <v>666</v>
       </c>
       <c r="J39" t="n">
-        <v>684</v>
+        <v>782</v>
       </c>
       <c r="K39" t="n">
-        <v>795</v>
+        <v>676</v>
       </c>
       <c r="L39" t="n">
-        <v>737.5</v>
+        <v>658.5</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>908</v>
+        <v>791</v>
       </c>
       <c r="C40" t="n">
-        <v>1017</v>
+        <v>889</v>
       </c>
       <c r="D40" t="n">
-        <v>832</v>
+        <v>771</v>
       </c>
       <c r="E40" t="n">
-        <v>774</v>
+        <v>792</v>
       </c>
       <c r="F40" t="n">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="G40" t="n">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="H40" t="n">
-        <v>951</v>
+        <v>725</v>
       </c>
       <c r="I40" t="n">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="J40" t="n">
-        <v>974</v>
+        <v>824</v>
       </c>
       <c r="K40" t="n">
-        <v>787</v>
+        <v>711</v>
       </c>
       <c r="L40" t="n">
-        <v>868</v>
+        <v>797.5</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>751</v>
+        <v>614</v>
       </c>
       <c r="C41" t="n">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="D41" t="n">
-        <v>795</v>
+        <v>633</v>
       </c>
       <c r="E41" t="n">
-        <v>766</v>
+        <v>707</v>
       </c>
       <c r="F41" t="n">
-        <v>824</v>
+        <v>734</v>
       </c>
       <c r="G41" t="n">
-        <v>728</v>
+        <v>676</v>
       </c>
       <c r="H41" t="n">
-        <v>850</v>
+        <v>609</v>
       </c>
       <c r="I41" t="n">
-        <v>828</v>
+        <v>782</v>
       </c>
       <c r="J41" t="n">
-        <v>904</v>
+        <v>747</v>
       </c>
       <c r="K41" t="n">
-        <v>784</v>
+        <v>688</v>
       </c>
       <c r="L41" t="n">
-        <v>802.8</v>
+        <v>698.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>807</v>
+        <v>780</v>
       </c>
       <c r="C42" t="n">
-        <v>832</v>
+        <v>703</v>
       </c>
       <c r="D42" t="n">
-        <v>704</v>
+        <v>744</v>
       </c>
       <c r="E42" t="n">
-        <v>843</v>
+        <v>616</v>
       </c>
       <c r="F42" t="n">
-        <v>917</v>
+        <v>716</v>
       </c>
       <c r="G42" t="n">
-        <v>713</v>
+        <v>647</v>
       </c>
       <c r="H42" t="n">
-        <v>763</v>
+        <v>804</v>
       </c>
       <c r="I42" t="n">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="J42" t="n">
-        <v>745</v>
+        <v>663</v>
       </c>
       <c r="K42" t="n">
-        <v>710</v>
+        <v>639</v>
       </c>
       <c r="L42" t="n">
-        <v>773.2</v>
+        <v>701.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>870</v>
+        <v>744</v>
       </c>
       <c r="C43" t="n">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="D43" t="n">
-        <v>808</v>
+        <v>753</v>
       </c>
       <c r="E43" t="n">
-        <v>925</v>
+        <v>863</v>
       </c>
       <c r="F43" t="n">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="G43" t="n">
-        <v>828</v>
+        <v>759</v>
       </c>
       <c r="H43" t="n">
-        <v>1012</v>
+        <v>866</v>
       </c>
       <c r="I43" t="n">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="J43" t="n">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="K43" t="n">
-        <v>930</v>
+        <v>943</v>
       </c>
       <c r="L43" t="n">
-        <v>861.5</v>
+        <v>816</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>771</v>
+        <v>794</v>
       </c>
       <c r="C44" t="n">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="D44" t="n">
-        <v>743</v>
+        <v>907</v>
       </c>
       <c r="E44" t="n">
-        <v>987</v>
+        <v>805</v>
       </c>
       <c r="F44" t="n">
-        <v>741</v>
+        <v>760</v>
       </c>
       <c r="G44" t="n">
-        <v>950</v>
+        <v>807</v>
       </c>
       <c r="H44" t="n">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="I44" t="n">
-        <v>866</v>
+        <v>710</v>
       </c>
       <c r="J44" t="n">
-        <v>839</v>
+        <v>774</v>
       </c>
       <c r="K44" t="n">
-        <v>857</v>
+        <v>792</v>
       </c>
       <c r="L44" t="n">
-        <v>822.4</v>
+        <v>783.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>820</v>
+        <v>590</v>
       </c>
       <c r="C45" t="n">
+        <v>747</v>
+      </c>
+      <c r="D45" t="n">
+        <v>617</v>
+      </c>
+      <c r="E45" t="n">
         <v>729</v>
       </c>
-      <c r="D45" t="n">
-        <v>732</v>
-      </c>
-      <c r="E45" t="n">
-        <v>771</v>
-      </c>
       <c r="F45" t="n">
-        <v>840</v>
+        <v>593</v>
       </c>
       <c r="G45" t="n">
-        <v>739</v>
+        <v>565</v>
       </c>
       <c r="H45" t="n">
-        <v>712</v>
+        <v>642</v>
       </c>
       <c r="I45" t="n">
-        <v>799</v>
+        <v>594</v>
       </c>
       <c r="J45" t="n">
-        <v>805</v>
+        <v>624</v>
       </c>
       <c r="K45" t="n">
-        <v>769</v>
+        <v>592</v>
       </c>
       <c r="L45" t="n">
-        <v>771.6</v>
+        <v>629.3</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>750</v>
+        <v>622</v>
       </c>
       <c r="C46" t="n">
-        <v>821</v>
+        <v>795</v>
       </c>
       <c r="D46" t="n">
-        <v>770</v>
+        <v>656</v>
       </c>
       <c r="E46" t="n">
-        <v>810</v>
+        <v>634</v>
       </c>
       <c r="F46" t="n">
-        <v>831</v>
+        <v>766</v>
       </c>
       <c r="G46" t="n">
-        <v>897</v>
+        <v>754</v>
       </c>
       <c r="H46" t="n">
-        <v>1009</v>
+        <v>703</v>
       </c>
       <c r="I46" t="n">
-        <v>890</v>
+        <v>730</v>
       </c>
       <c r="J46" t="n">
-        <v>837</v>
+        <v>733</v>
       </c>
       <c r="K46" t="n">
-        <v>858</v>
+        <v>654</v>
       </c>
       <c r="L46" t="n">
-        <v>847.3</v>
+        <v>704.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1004</v>
+        <v>800</v>
       </c>
       <c r="C47" t="n">
-        <v>1008</v>
+        <v>779</v>
       </c>
       <c r="D47" t="n">
-        <v>855</v>
+        <v>769</v>
       </c>
       <c r="E47" t="n">
-        <v>897</v>
+        <v>791</v>
       </c>
       <c r="F47" t="n">
-        <v>848</v>
+        <v>793</v>
       </c>
       <c r="G47" t="n">
-        <v>848</v>
+        <v>783</v>
       </c>
       <c r="H47" t="n">
-        <v>899</v>
+        <v>788</v>
       </c>
       <c r="I47" t="n">
-        <v>896</v>
+        <v>664</v>
       </c>
       <c r="J47" t="n">
-        <v>950</v>
+        <v>760</v>
       </c>
       <c r="K47" t="n">
-        <v>817</v>
+        <v>883</v>
       </c>
       <c r="L47" t="n">
-        <v>902.2</v>
+        <v>781</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>774</v>
+        <v>586</v>
       </c>
       <c r="C48" t="n">
-        <v>820</v>
+        <v>755</v>
       </c>
       <c r="D48" t="n">
-        <v>778</v>
+        <v>721</v>
       </c>
       <c r="E48" t="n">
-        <v>895</v>
+        <v>669</v>
       </c>
       <c r="F48" t="n">
-        <v>862</v>
+        <v>739</v>
       </c>
       <c r="G48" t="n">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="H48" t="n">
-        <v>731</v>
+        <v>673</v>
       </c>
       <c r="I48" t="n">
-        <v>675</v>
+        <v>749</v>
       </c>
       <c r="J48" t="n">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="K48" t="n">
-        <v>777</v>
+        <v>671</v>
       </c>
       <c r="L48" t="n">
-        <v>783.8</v>
+        <v>711</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1088</v>
+        <v>779</v>
       </c>
       <c r="C49" t="n">
-        <v>953</v>
+        <v>802</v>
       </c>
       <c r="D49" t="n">
-        <v>945</v>
+        <v>897</v>
       </c>
       <c r="E49" t="n">
-        <v>1068</v>
+        <v>827</v>
       </c>
       <c r="F49" t="n">
-        <v>947</v>
+        <v>752</v>
       </c>
       <c r="G49" t="n">
-        <v>845</v>
+        <v>779</v>
       </c>
       <c r="H49" t="n">
-        <v>850</v>
+        <v>915</v>
       </c>
       <c r="I49" t="n">
-        <v>913</v>
+        <v>848</v>
       </c>
       <c r="J49" t="n">
-        <v>984</v>
+        <v>873</v>
       </c>
       <c r="K49" t="n">
-        <v>895</v>
+        <v>779</v>
       </c>
       <c r="L49" t="n">
-        <v>948.8</v>
+        <v>825.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>822</v>
+        <v>619</v>
       </c>
       <c r="C50" t="n">
-        <v>912</v>
+        <v>639</v>
       </c>
       <c r="D50" t="n">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="E50" t="n">
-        <v>689</v>
+        <v>734</v>
       </c>
       <c r="F50" t="n">
-        <v>764</v>
+        <v>714</v>
       </c>
       <c r="G50" t="n">
-        <v>692</v>
+        <v>664</v>
       </c>
       <c r="H50" t="n">
-        <v>676</v>
+        <v>721</v>
       </c>
       <c r="I50" t="n">
-        <v>680</v>
+        <v>648</v>
       </c>
       <c r="J50" t="n">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="K50" t="n">
-        <v>677</v>
+        <v>624</v>
       </c>
       <c r="L50" t="n">
-        <v>736</v>
+        <v>676.2</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>726</v>
+        <v>694</v>
       </c>
       <c r="C51" t="n">
-        <v>900</v>
+        <v>740</v>
       </c>
       <c r="D51" t="n">
-        <v>749</v>
+        <v>806</v>
       </c>
       <c r="E51" t="n">
-        <v>859</v>
+        <v>733</v>
       </c>
       <c r="F51" t="n">
-        <v>734</v>
+        <v>710</v>
       </c>
       <c r="G51" t="n">
-        <v>785</v>
+        <v>687</v>
       </c>
       <c r="H51" t="n">
-        <v>783</v>
+        <v>667</v>
       </c>
       <c r="I51" t="n">
-        <v>722</v>
+        <v>735</v>
       </c>
       <c r="J51" t="n">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="K51" t="n">
-        <v>766</v>
+        <v>691</v>
       </c>
       <c r="L51" t="n">
-        <v>780.1</v>
+        <v>723.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>810.22</v>
+        <v>724.76</v>
       </c>
       <c r="C52" t="n">
-        <v>836.64</v>
+        <v>743.66</v>
       </c>
       <c r="D52" t="n">
-        <v>810.58</v>
+        <v>730.8</v>
       </c>
       <c r="E52" t="n">
-        <v>824.24</v>
+        <v>744.7</v>
       </c>
       <c r="F52" t="n">
-        <v>823.26</v>
+        <v>739.62</v>
       </c>
       <c r="G52" t="n">
-        <v>793.96</v>
+        <v>733.9</v>
       </c>
       <c r="H52" t="n">
-        <v>813.62</v>
+        <v>743.8200000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>818.28</v>
+        <v>739.84</v>
       </c>
       <c r="J52" t="n">
-        <v>821.4</v>
+        <v>741.7</v>
       </c>
       <c r="K52" t="n">
-        <v>811.78</v>
+        <v>747.48</v>
       </c>
       <c r="L52" t="n">
-        <v>816.398</v>
+        <v>739.0279999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.613242149353027</v>
+        <v>4.228075504302979</v>
       </c>
       <c r="C2" t="n">
-        <v>4.330467224121094</v>
+        <v>4.457542419433594</v>
       </c>
       <c r="D2" t="n">
-        <v>5.131956577301025</v>
+        <v>4.159680843353271</v>
       </c>
       <c r="E2" t="n">
-        <v>4.134965658187866</v>
+        <v>4.950168371200562</v>
       </c>
       <c r="F2" t="n">
-        <v>4.913000106811523</v>
+        <v>4.220436811447144</v>
       </c>
       <c r="G2" t="n">
-        <v>4.353408098220825</v>
+        <v>4.044538974761963</v>
       </c>
       <c r="H2" t="n">
-        <v>4.162405252456665</v>
+        <v>4.24362850189209</v>
       </c>
       <c r="I2" t="n">
-        <v>4.36735987663269</v>
+        <v>3.865239858627319</v>
       </c>
       <c r="J2" t="n">
-        <v>4.706496477127075</v>
+        <v>4.169433832168579</v>
       </c>
       <c r="K2" t="n">
-        <v>4.154434680938721</v>
+        <v>3.995323896408081</v>
       </c>
       <c r="L2" t="n">
-        <v>4.486773610115051</v>
+        <v>4.233406901359558</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.510000228881836</v>
+        <v>4.968870401382446</v>
       </c>
       <c r="C3" t="n">
-        <v>5.624653100967407</v>
+        <v>4.8830726146698</v>
       </c>
       <c r="D3" t="n">
-        <v>5.007230281829834</v>
+        <v>4.345459461212158</v>
       </c>
       <c r="E3" t="n">
-        <v>4.713482618331909</v>
+        <v>4.67162013053894</v>
       </c>
       <c r="F3" t="n">
-        <v>4.505027532577515</v>
+        <v>4.640199899673462</v>
       </c>
       <c r="G3" t="n">
-        <v>4.772323131561279</v>
+        <v>4.423803567886353</v>
       </c>
       <c r="H3" t="n">
-        <v>4.643666744232178</v>
+        <v>4.677587747573853</v>
       </c>
       <c r="I3" t="n">
-        <v>5.089553117752075</v>
+        <v>4.443705797195435</v>
       </c>
       <c r="J3" t="n">
-        <v>5.074066638946533</v>
+        <v>4.59131932258606</v>
       </c>
       <c r="K3" t="n">
-        <v>5.143890142440796</v>
+        <v>4.397812604904175</v>
       </c>
       <c r="L3" t="n">
-        <v>4.908389353752137</v>
+        <v>4.604345154762268</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.323476076126099</v>
+        <v>5.459112644195557</v>
       </c>
       <c r="C4" t="n">
-        <v>4.569845914840698</v>
+        <v>4.891071319580078</v>
       </c>
       <c r="D4" t="n">
-        <v>5.394256114959717</v>
+        <v>4.436713457107544</v>
       </c>
       <c r="E4" t="n">
-        <v>4.914985418319702</v>
+        <v>5.935271739959717</v>
       </c>
       <c r="F4" t="n">
-        <v>5.113466024398804</v>
+        <v>5.755642175674438</v>
       </c>
       <c r="G4" t="n">
-        <v>4.706516742706299</v>
+        <v>5.542826414108276</v>
       </c>
       <c r="H4" t="n">
-        <v>4.988307952880859</v>
+        <v>5.096823215484619</v>
       </c>
       <c r="I4" t="n">
-        <v>4.572334051132202</v>
+        <v>5.520696401596069</v>
       </c>
       <c r="J4" t="n">
-        <v>5.112556934356689</v>
+        <v>5.265152215957642</v>
       </c>
       <c r="K4" t="n">
-        <v>5.043163299560547</v>
+        <v>4.522001266479492</v>
       </c>
       <c r="L4" t="n">
-        <v>4.873890852928161</v>
+        <v>5.242531085014344</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.440135478973389</v>
+        <v>5.542221784591675</v>
       </c>
       <c r="C5" t="n">
-        <v>5.151881694793701</v>
+        <v>5.852412700653076</v>
       </c>
       <c r="D5" t="n">
-        <v>5.326940298080444</v>
+        <v>5.518214225769043</v>
       </c>
       <c r="E5" t="n">
-        <v>5.138386249542236</v>
+        <v>5.001108407974243</v>
       </c>
       <c r="F5" t="n">
-        <v>5.616696357727051</v>
+        <v>5.217466592788696</v>
       </c>
       <c r="G5" t="n">
-        <v>5.920388698577881</v>
+        <v>5.016962289810181</v>
       </c>
       <c r="H5" t="n">
-        <v>5.149886608123779</v>
+        <v>5.106276035308838</v>
       </c>
       <c r="I5" t="n">
-        <v>5.675979852676392</v>
+        <v>5.112226963043213</v>
       </c>
       <c r="J5" t="n">
-        <v>4.908727169036865</v>
+        <v>4.717774629592896</v>
       </c>
       <c r="K5" t="n">
-        <v>5.284745693206787</v>
+        <v>4.912103891372681</v>
       </c>
       <c r="L5" t="n">
-        <v>5.361376810073852</v>
+        <v>5.199676752090454</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.708847999572754</v>
+        <v>3.997823238372803</v>
       </c>
       <c r="C6" t="n">
-        <v>4.18012261390686</v>
+        <v>3.842803716659546</v>
       </c>
       <c r="D6" t="n">
-        <v>4.073395490646362</v>
+        <v>3.924364328384399</v>
       </c>
       <c r="E6" t="n">
-        <v>3.608605146408081</v>
+        <v>3.596824407577515</v>
       </c>
       <c r="F6" t="n">
-        <v>3.759223222732544</v>
+        <v>3.68512487411499</v>
       </c>
       <c r="G6" t="n">
-        <v>3.87342357635498</v>
+        <v>4.264657020568848</v>
       </c>
       <c r="H6" t="n">
-        <v>3.738758087158203</v>
+        <v>4.611037731170654</v>
       </c>
       <c r="I6" t="n">
-        <v>4.16265344619751</v>
+        <v>4.101361036300659</v>
       </c>
       <c r="J6" t="n">
-        <v>3.768206357955933</v>
+        <v>4.385750532150269</v>
       </c>
       <c r="K6" t="n">
-        <v>3.621570348739624</v>
+        <v>4.508056640625</v>
       </c>
       <c r="L6" t="n">
-        <v>3.849480628967285</v>
+        <v>4.091780352592468</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>5.209428787231445</v>
+        <v>5.195917844772339</v>
       </c>
       <c r="C7" t="n">
-        <v>4.965116262435913</v>
+        <v>5.072598695755005</v>
       </c>
       <c r="D7" t="n">
-        <v>5.083758354187012</v>
+        <v>4.618246078491211</v>
       </c>
       <c r="E7" t="n">
-        <v>5.079275846481323</v>
+        <v>5.106502532958984</v>
       </c>
       <c r="F7" t="n">
-        <v>5.263790845870972</v>
+        <v>4.785332202911377</v>
       </c>
       <c r="G7" t="n">
-        <v>4.750181674957275</v>
+        <v>4.760379076004028</v>
       </c>
       <c r="H7" t="n">
-        <v>4.632930755615234</v>
+        <v>4.867130517959595</v>
       </c>
       <c r="I7" t="n">
-        <v>4.789548397064209</v>
+        <v>4.620141267776489</v>
       </c>
       <c r="J7" t="n">
-        <v>5.350560426712036</v>
+        <v>5.15192437171936</v>
       </c>
       <c r="K7" t="n">
-        <v>5.417402982711792</v>
+        <v>4.610006332397461</v>
       </c>
       <c r="L7" t="n">
-        <v>5.054199433326721</v>
+        <v>4.878817892074585</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.624561786651611</v>
+        <v>3.775192975997925</v>
       </c>
       <c r="C8" t="n">
-        <v>4.270869970321655</v>
+        <v>3.700871467590332</v>
       </c>
       <c r="D8" t="n">
-        <v>4.185111045837402</v>
+        <v>3.720876932144165</v>
       </c>
       <c r="E8" t="n">
-        <v>4.282354593276978</v>
+        <v>4.660787582397461</v>
       </c>
       <c r="F8" t="n">
-        <v>3.700866937637329</v>
+        <v>3.813273668289185</v>
       </c>
       <c r="G8" t="n">
-        <v>4.367128133773804</v>
+        <v>3.913552761077881</v>
       </c>
       <c r="H8" t="n">
-        <v>3.914306163787842</v>
+        <v>3.939985990524292</v>
       </c>
       <c r="I8" t="n">
-        <v>3.922781467437744</v>
+        <v>3.884613037109375</v>
       </c>
       <c r="J8" t="n">
-        <v>4.831429719924927</v>
+        <v>3.810299634933472</v>
       </c>
       <c r="K8" t="n">
-        <v>4.197083473205566</v>
+        <v>3.876659870147705</v>
       </c>
       <c r="L8" t="n">
-        <v>4.129649329185486</v>
+        <v>3.909611392021179</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.786629676818848</v>
+        <v>3.591655492782593</v>
       </c>
       <c r="C9" t="n">
-        <v>4.166078090667725</v>
+        <v>3.718945503234863</v>
       </c>
       <c r="D9" t="n">
-        <v>4.241949558258057</v>
+        <v>4.085873126983643</v>
       </c>
       <c r="E9" t="n">
-        <v>3.840508222579956</v>
+        <v>4.070937395095825</v>
       </c>
       <c r="F9" t="n">
-        <v>3.970155477523804</v>
+        <v>3.963901996612549</v>
       </c>
       <c r="G9" t="n">
-        <v>3.940752029418945</v>
+        <v>4.479382753372192</v>
       </c>
       <c r="H9" t="n">
-        <v>4.070404052734375</v>
+        <v>3.987647294998169</v>
       </c>
       <c r="I9" t="n">
-        <v>4.004568338394165</v>
+        <v>4.101843118667603</v>
       </c>
       <c r="J9" t="n">
-        <v>4.120772361755371</v>
+        <v>4.025846481323242</v>
       </c>
       <c r="K9" t="n">
-        <v>3.655359745025635</v>
+        <v>3.691951274871826</v>
       </c>
       <c r="L9" t="n">
-        <v>3.979717755317688</v>
+        <v>3.97179844379425</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.23036789894104</v>
+        <v>4.606876850128174</v>
       </c>
       <c r="C10" t="n">
-        <v>5.816857099533081</v>
+        <v>4.90351939201355</v>
       </c>
       <c r="D10" t="n">
-        <v>5.704679250717163</v>
+        <v>4.777855634689331</v>
       </c>
       <c r="E10" t="n">
-        <v>5.09777569770813</v>
+        <v>4.535953283309937</v>
       </c>
       <c r="F10" t="n">
-        <v>5.366316795349121</v>
+        <v>4.790554046630859</v>
       </c>
       <c r="G10" t="n">
-        <v>5.493970632553101</v>
+        <v>5.652159452438354</v>
       </c>
       <c r="H10" t="n">
-        <v>5.654576301574707</v>
+        <v>5.53643798828125</v>
       </c>
       <c r="I10" t="n">
-        <v>5.484541654586792</v>
+        <v>4.688619613647461</v>
       </c>
       <c r="J10" t="n">
-        <v>5.189281225204468</v>
+        <v>5.048358917236328</v>
       </c>
       <c r="K10" t="n">
-        <v>5.205727338790894</v>
+        <v>4.901040315628052</v>
       </c>
       <c r="L10" t="n">
-        <v>5.42440938949585</v>
+        <v>4.944137549400329</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.419738531112671</v>
+        <v>4.471112966537476</v>
       </c>
       <c r="C11" t="n">
-        <v>5.127427339553833</v>
+        <v>4.717907190322876</v>
       </c>
       <c r="D11" t="n">
-        <v>4.663114547729492</v>
+        <v>4.819469928741455</v>
       </c>
       <c r="E11" t="n">
-        <v>4.542424440383911</v>
+        <v>4.582099199295044</v>
       </c>
       <c r="F11" t="n">
-        <v>4.868616580963135</v>
+        <v>4.34320592880249</v>
       </c>
       <c r="G11" t="n">
-        <v>4.665663242340088</v>
+        <v>4.773093223571777</v>
       </c>
       <c r="H11" t="n">
-        <v>4.465597867965698</v>
+        <v>4.383603811264038</v>
       </c>
       <c r="I11" t="n">
-        <v>4.688563108444214</v>
+        <v>4.651416301727295</v>
       </c>
       <c r="J11" t="n">
-        <v>5.118444442749023</v>
+        <v>4.213059902191162</v>
       </c>
       <c r="K11" t="n">
-        <v>4.601273775100708</v>
+        <v>4.59058690071106</v>
       </c>
       <c r="L11" t="n">
-        <v>4.716086387634277</v>
+        <v>4.554555535316467</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.194333553314209</v>
+        <v>4.29589581489563</v>
       </c>
       <c r="C12" t="n">
-        <v>4.229221343994141</v>
+        <v>4.143242835998535</v>
       </c>
       <c r="D12" t="n">
-        <v>4.070137500762939</v>
+        <v>3.732786893844604</v>
       </c>
       <c r="E12" t="n">
-        <v>3.770867824554443</v>
+        <v>4.233997106552124</v>
       </c>
       <c r="F12" t="n">
-        <v>4.00379204750061</v>
+        <v>4.319987058639526</v>
       </c>
       <c r="G12" t="n">
-        <v>3.599834203720093</v>
+        <v>4.066205263137817</v>
       </c>
       <c r="H12" t="n">
-        <v>4.244706392288208</v>
+        <v>4.447612762451172</v>
       </c>
       <c r="I12" t="n">
-        <v>4.207282304763794</v>
+        <v>3.788391828536987</v>
       </c>
       <c r="J12" t="n">
-        <v>4.082590818405151</v>
+        <v>4.357924699783325</v>
       </c>
       <c r="K12" t="n">
-        <v>3.936979055404663</v>
+        <v>4.137946605682373</v>
       </c>
       <c r="L12" t="n">
-        <v>4.033974504470825</v>
+        <v>4.15239908695221</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.426725625991821</v>
+        <v>3.839211463928223</v>
       </c>
       <c r="C13" t="n">
-        <v>3.935474395751953</v>
+        <v>4.098097324371338</v>
       </c>
       <c r="D13" t="n">
-        <v>4.61624002456665</v>
+        <v>4.580325841903687</v>
       </c>
       <c r="E13" t="n">
-        <v>4.211267948150635</v>
+        <v>4.352441549301147</v>
       </c>
       <c r="F13" t="n">
-        <v>4.053168058395386</v>
+        <v>4.235503435134888</v>
       </c>
       <c r="G13" t="n">
-        <v>3.853645086288452</v>
+        <v>4.106854438781738</v>
       </c>
       <c r="H13" t="n">
-        <v>4.809520483016968</v>
+        <v>3.939836263656616</v>
       </c>
       <c r="I13" t="n">
-        <v>4.048979520797729</v>
+        <v>4.59106969833374</v>
       </c>
       <c r="J13" t="n">
-        <v>4.114769697189331</v>
+        <v>4.471378803253174</v>
       </c>
       <c r="K13" t="n">
-        <v>4.069395780563354</v>
+        <v>3.817062616348267</v>
       </c>
       <c r="L13" t="n">
-        <v>4.213918662071228</v>
+        <v>4.203178143501281</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.36264443397522</v>
+        <v>4.165176868438721</v>
       </c>
       <c r="C14" t="n">
-        <v>3.989619970321655</v>
+        <v>3.784169912338257</v>
       </c>
       <c r="D14" t="n">
-        <v>4.087873458862305</v>
+        <v>4.109841585159302</v>
       </c>
       <c r="E14" t="n">
-        <v>4.106815576553345</v>
+        <v>4.003588914871216</v>
       </c>
       <c r="F14" t="n">
-        <v>4.511756658554077</v>
+        <v>4.128778219223022</v>
       </c>
       <c r="G14" t="n">
-        <v>4.568603515625</v>
+        <v>3.937254905700684</v>
       </c>
       <c r="H14" t="n">
-        <v>3.848499298095703</v>
+        <v>3.982650756835938</v>
       </c>
       <c r="I14" t="n">
-        <v>4.071390867233276</v>
+        <v>3.726803064346313</v>
       </c>
       <c r="J14" t="n">
-        <v>4.343683958053589</v>
+        <v>4.699342012405396</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0474693775177</v>
+        <v>3.744764566421509</v>
       </c>
       <c r="L14" t="n">
-        <v>4.193835711479187</v>
+        <v>4.028237080574035</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>5.079275608062744</v>
+        <v>4.803521871566772</v>
       </c>
       <c r="C15" t="n">
-        <v>4.727185249328613</v>
+        <v>5.144719123840332</v>
       </c>
       <c r="D15" t="n">
-        <v>4.445424795150757</v>
+        <v>4.441444158554077</v>
       </c>
       <c r="E15" t="n">
-        <v>4.633445501327515</v>
+        <v>4.532786130905151</v>
       </c>
       <c r="F15" t="n">
-        <v>5.013962030410767</v>
+        <v>4.486870050430298</v>
       </c>
       <c r="G15" t="n">
-        <v>4.551671504974365</v>
+        <v>4.516767501831055</v>
       </c>
       <c r="H15" t="n">
-        <v>4.742169141769409</v>
+        <v>4.410087585449219</v>
       </c>
       <c r="I15" t="n">
-        <v>4.864841938018799</v>
+        <v>4.789980173110962</v>
       </c>
       <c r="J15" t="n">
-        <v>5.014959573745728</v>
+        <v>5.708863735198975</v>
       </c>
       <c r="K15" t="n">
-        <v>4.712251663208008</v>
+        <v>5.627856492996216</v>
       </c>
       <c r="L15" t="n">
-        <v>4.778518700599671</v>
+        <v>4.846289682388305</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.213037252426147</v>
+        <v>4.968436479568481</v>
       </c>
       <c r="C16" t="n">
-        <v>4.50679349899292</v>
+        <v>5.544238567352295</v>
       </c>
       <c r="D16" t="n">
-        <v>4.533684492111206</v>
+        <v>4.534517288208008</v>
       </c>
       <c r="E16" t="n">
-        <v>4.770583391189575</v>
+        <v>4.122954607009888</v>
       </c>
       <c r="F16" t="n">
-        <v>4.822322130203247</v>
+        <v>4.004809379577637</v>
       </c>
       <c r="G16" t="n">
-        <v>4.696544170379639</v>
+        <v>4.321794271469116</v>
       </c>
       <c r="H16" t="n">
-        <v>4.84269380569458</v>
+        <v>4.42949366569519</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3055260181427</v>
+        <v>4.442489862442017</v>
       </c>
       <c r="J16" t="n">
-        <v>5.281068801879883</v>
+        <v>4.517758131027222</v>
       </c>
       <c r="K16" t="n">
-        <v>4.496045827865601</v>
+        <v>4.328801870346069</v>
       </c>
       <c r="L16" t="n">
-        <v>4.646829938888549</v>
+        <v>4.521529412269592</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.764372110366821</v>
+        <v>5.352335453033447</v>
       </c>
       <c r="C17" t="n">
-        <v>4.74094557762146</v>
+        <v>4.639956712722778</v>
       </c>
       <c r="D17" t="n">
-        <v>4.296057462692261</v>
+        <v>3.954715728759766</v>
       </c>
       <c r="E17" t="n">
-        <v>4.610274791717529</v>
+        <v>4.179147243499756</v>
       </c>
       <c r="F17" t="n">
-        <v>5.394346237182617</v>
+        <v>5.302260637283325</v>
       </c>
       <c r="G17" t="n">
-        <v>5.434809684753418</v>
+        <v>4.698640584945679</v>
       </c>
       <c r="H17" t="n">
-        <v>4.138928651809692</v>
+        <v>4.173150062561035</v>
       </c>
       <c r="I17" t="n">
-        <v>4.448681354522705</v>
+        <v>4.611716508865356</v>
       </c>
       <c r="J17" t="n">
-        <v>4.368863582611084</v>
+        <v>4.353835821151733</v>
       </c>
       <c r="K17" t="n">
-        <v>5.098536252975464</v>
+        <v>4.454478740692139</v>
       </c>
       <c r="L17" t="n">
-        <v>4.729581570625305</v>
+        <v>4.572023749351501</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>3.769880771636963</v>
+        <v>4.190232515335083</v>
       </c>
       <c r="C18" t="n">
-        <v>4.182373046875</v>
+        <v>4.103068351745605</v>
       </c>
       <c r="D18" t="n">
-        <v>3.868657350540161</v>
+        <v>3.963930130004883</v>
       </c>
       <c r="E18" t="n">
-        <v>3.92648983001709</v>
+        <v>4.224266290664673</v>
       </c>
       <c r="F18" t="n">
-        <v>4.05765175819397</v>
+        <v>3.884685516357422</v>
       </c>
       <c r="G18" t="n">
-        <v>3.765404939651489</v>
+        <v>3.979876756668091</v>
       </c>
       <c r="H18" t="n">
-        <v>3.71305513381958</v>
+        <v>4.02849555015564</v>
       </c>
       <c r="I18" t="n">
-        <v>3.722014665603638</v>
+        <v>4.004792451858521</v>
       </c>
       <c r="J18" t="n">
-        <v>3.793326377868652</v>
+        <v>4.143843650817871</v>
       </c>
       <c r="K18" t="n">
-        <v>3.893574237823486</v>
+        <v>4.232278347015381</v>
       </c>
       <c r="L18" t="n">
-        <v>3.869242811203003</v>
+        <v>4.075546956062317</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.663620710372925</v>
+        <v>5.003350734710693</v>
       </c>
       <c r="C19" t="n">
-        <v>4.452630758285522</v>
+        <v>4.517987728118896</v>
       </c>
       <c r="D19" t="n">
-        <v>4.905012130737305</v>
+        <v>4.561394929885864</v>
       </c>
       <c r="E19" t="n">
-        <v>4.882064580917358</v>
+        <v>4.57286810874939</v>
       </c>
       <c r="F19" t="n">
-        <v>4.377328395843506</v>
+        <v>4.928083181381226</v>
       </c>
       <c r="G19" t="n">
-        <v>4.607288599014282</v>
+        <v>4.968152046203613</v>
       </c>
       <c r="H19" t="n">
-        <v>4.669636487960815</v>
+        <v>4.639839649200439</v>
       </c>
       <c r="I19" t="n">
-        <v>4.821705341339111</v>
+        <v>4.259688377380371</v>
       </c>
       <c r="J19" t="n">
-        <v>6.08083963394165</v>
+        <v>4.461666107177734</v>
       </c>
       <c r="K19" t="n">
-        <v>4.37613582611084</v>
+        <v>4.905057907104492</v>
       </c>
       <c r="L19" t="n">
-        <v>4.783626246452331</v>
+        <v>4.681808876991272</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.498782396316528</v>
+        <v>4.127836942672729</v>
       </c>
       <c r="C20" t="n">
-        <v>4.800508975982666</v>
+        <v>4.712542295455933</v>
       </c>
       <c r="D20" t="n">
-        <v>4.172169923782349</v>
+        <v>4.069651126861572</v>
       </c>
       <c r="E20" t="n">
-        <v>4.646894454956055</v>
+        <v>4.629306554794312</v>
       </c>
       <c r="F20" t="n">
-        <v>4.462883949279785</v>
+        <v>4.681620359420776</v>
       </c>
       <c r="G20" t="n">
-        <v>4.610003471374512</v>
+        <v>5.087578058242798</v>
       </c>
       <c r="H20" t="n">
-        <v>4.922676086425781</v>
+        <v>4.937924861907959</v>
       </c>
       <c r="I20" t="n">
-        <v>5.286736011505127</v>
+        <v>4.270674228668213</v>
       </c>
       <c r="J20" t="n">
-        <v>4.988533735275269</v>
+        <v>4.497168302536011</v>
       </c>
       <c r="K20" t="n">
-        <v>5.629844188690186</v>
+        <v>4.531181812286377</v>
       </c>
       <c r="L20" t="n">
-        <v>4.801903319358826</v>
+        <v>4.554548454284668</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.290815591812134</v>
+        <v>4.63133716583252</v>
       </c>
       <c r="C21" t="n">
-        <v>4.388611078262329</v>
+        <v>4.573363542556763</v>
       </c>
       <c r="D21" t="n">
-        <v>4.411512851715088</v>
+        <v>4.145941734313965</v>
       </c>
       <c r="E21" t="n">
-        <v>5.048381567001343</v>
+        <v>4.412234306335449</v>
       </c>
       <c r="F21" t="n">
-        <v>4.816492795944214</v>
+        <v>4.448555469512939</v>
       </c>
       <c r="G21" t="n">
-        <v>4.921738386154175</v>
+        <v>4.788569927215576</v>
       </c>
       <c r="H21" t="n">
-        <v>4.70408034324646</v>
+        <v>4.238800525665283</v>
       </c>
       <c r="I21" t="n">
-        <v>4.429713487625122</v>
+        <v>4.175859928131104</v>
       </c>
       <c r="J21" t="n">
-        <v>4.738434314727783</v>
+        <v>4.317518711090088</v>
       </c>
       <c r="K21" t="n">
-        <v>4.647669315338135</v>
+        <v>4.316519975662231</v>
       </c>
       <c r="L21" t="n">
-        <v>4.639744973182678</v>
+        <v>4.404870128631591</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.435694217681885</v>
+        <v>4.098546504974365</v>
       </c>
       <c r="C22" t="n">
-        <v>4.622229814529419</v>
+        <v>3.818786144256592</v>
       </c>
       <c r="D22" t="n">
-        <v>4.00778865814209</v>
+        <v>4.125126123428345</v>
       </c>
       <c r="E22" t="n">
-        <v>3.876628637313843</v>
+        <v>3.947244167327881</v>
       </c>
       <c r="F22" t="n">
-        <v>4.36237096786499</v>
+        <v>3.957720994949341</v>
       </c>
       <c r="G22" t="n">
-        <v>4.257645130157471</v>
+        <v>3.881914615631104</v>
       </c>
       <c r="H22" t="n">
-        <v>4.440675020217896</v>
+        <v>4.10859227180481</v>
       </c>
       <c r="I22" t="n">
-        <v>4.462146997451782</v>
+        <v>3.954946994781494</v>
       </c>
       <c r="J22" t="n">
-        <v>5.136397838592529</v>
+        <v>4.279395818710327</v>
       </c>
       <c r="K22" t="n">
-        <v>4.546910047531128</v>
+        <v>4.324316740036011</v>
       </c>
       <c r="L22" t="n">
-        <v>4.414848732948303</v>
+        <v>4.049659037590027</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.915976285934448</v>
+        <v>4.444458484649658</v>
       </c>
       <c r="C23" t="n">
-        <v>4.523970127105713</v>
+        <v>4.311305522918701</v>
       </c>
       <c r="D23" t="n">
-        <v>4.689121007919312</v>
+        <v>4.073950529098511</v>
       </c>
       <c r="E23" t="n">
-        <v>4.46412205696106</v>
+        <v>4.169690608978271</v>
       </c>
       <c r="F23" t="n">
-        <v>4.583840608596802</v>
+        <v>4.636468887329102</v>
       </c>
       <c r="G23" t="n">
-        <v>4.476501941680908</v>
+        <v>4.616000652313232</v>
       </c>
       <c r="H23" t="n">
-        <v>4.627946376800537</v>
+        <v>4.953854322433472</v>
       </c>
       <c r="I23" t="n">
-        <v>4.920684099197388</v>
+        <v>4.452253818511963</v>
       </c>
       <c r="J23" t="n">
-        <v>4.431967735290527</v>
+        <v>4.287328958511353</v>
       </c>
       <c r="K23" t="n">
-        <v>4.037499904632568</v>
+        <v>4.788612365722656</v>
       </c>
       <c r="L23" t="n">
-        <v>4.567163014411927</v>
+        <v>4.473392415046692</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>3.840025663375854</v>
+        <v>4.322287559509277</v>
       </c>
       <c r="C24" t="n">
-        <v>4.657377004623413</v>
+        <v>4.831429719924927</v>
       </c>
       <c r="D24" t="n">
-        <v>4.270888566970825</v>
+        <v>5.506534814834595</v>
       </c>
       <c r="E24" t="n">
-        <v>4.936153173446655</v>
+        <v>4.578845262527466</v>
       </c>
       <c r="F24" t="n">
-        <v>4.365129709243774</v>
+        <v>4.25766134262085</v>
       </c>
       <c r="G24" t="n">
-        <v>3.983635663986206</v>
+        <v>3.955447196960449</v>
       </c>
       <c r="H24" t="n">
-        <v>3.860950469970703</v>
+        <v>4.012803554534912</v>
       </c>
       <c r="I24" t="n">
-        <v>4.340701103210449</v>
+        <v>4.576342344284058</v>
       </c>
       <c r="J24" t="n">
-        <v>5.029937028884888</v>
+        <v>4.284659385681152</v>
       </c>
       <c r="K24" t="n">
-        <v>4.243949413299561</v>
+        <v>4.457624197006226</v>
       </c>
       <c r="L24" t="n">
-        <v>4.352874779701233</v>
+        <v>4.478363537788391</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>3.65301775932312</v>
+        <v>3.472647905349731</v>
       </c>
       <c r="C25" t="n">
-        <v>4.174147367477417</v>
+        <v>4.03671932220459</v>
       </c>
       <c r="D25" t="n">
-        <v>3.799597024917603</v>
+        <v>3.755441188812256</v>
       </c>
       <c r="E25" t="n">
-        <v>4.00605845451355</v>
+        <v>3.820183992385864</v>
       </c>
       <c r="F25" t="n">
-        <v>3.628274440765381</v>
+        <v>4.02873706817627</v>
       </c>
       <c r="G25" t="n">
-        <v>3.992320537567139</v>
+        <v>3.88055419921875</v>
       </c>
       <c r="H25" t="n">
-        <v>3.859678268432617</v>
+        <v>3.964214563369751</v>
       </c>
       <c r="I25" t="n">
-        <v>3.903554201126099</v>
+        <v>4.134686946868896</v>
       </c>
       <c r="J25" t="n">
-        <v>4.301547765731812</v>
+        <v>4.714549779891968</v>
       </c>
       <c r="K25" t="n">
-        <v>4.014754772186279</v>
+        <v>3.76185941696167</v>
       </c>
       <c r="L25" t="n">
-        <v>3.933295059204101</v>
+        <v>3.956959438323975</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.225232362747192</v>
+        <v>4.486110210418701</v>
       </c>
       <c r="C26" t="n">
-        <v>4.358891010284424</v>
+        <v>4.535049438476562</v>
       </c>
       <c r="D26" t="n">
-        <v>5.179321765899658</v>
+        <v>4.557181358337402</v>
       </c>
       <c r="E26" t="n">
-        <v>4.283580780029297</v>
+        <v>4.425766468048096</v>
       </c>
       <c r="F26" t="n">
-        <v>4.732444047927856</v>
+        <v>4.321492195129395</v>
       </c>
       <c r="G26" t="n">
-        <v>4.501051664352417</v>
+        <v>4.327482223510742</v>
       </c>
       <c r="H26" t="n">
-        <v>4.607264041900635</v>
+        <v>4.430241107940674</v>
       </c>
       <c r="I26" t="n">
-        <v>4.623225212097168</v>
+        <v>4.668006658554077</v>
       </c>
       <c r="J26" t="n">
-        <v>5.04065465927124</v>
+        <v>5.02527904510498</v>
       </c>
       <c r="K26" t="n">
-        <v>4.868591785430908</v>
+        <v>4.779901742935181</v>
       </c>
       <c r="L26" t="n">
-        <v>4.64202573299408</v>
+        <v>4.555651044845581</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>5.117441415786743</v>
+        <v>4.678507089614868</v>
       </c>
       <c r="C27" t="n">
-        <v>4.523991346359253</v>
+        <v>5.090448141098022</v>
       </c>
       <c r="D27" t="n">
-        <v>5.363321781158447</v>
+        <v>4.580588817596436</v>
       </c>
       <c r="E27" t="n">
-        <v>5.162348508834839</v>
+        <v>4.853317260742188</v>
       </c>
       <c r="F27" t="n">
-        <v>5.148412466049194</v>
+        <v>5.030215263366699</v>
       </c>
       <c r="G27" t="n">
-        <v>5.295017957687378</v>
+        <v>4.84765625</v>
       </c>
       <c r="H27" t="n">
-        <v>5.564336061477661</v>
+        <v>4.532496452331543</v>
       </c>
       <c r="I27" t="n">
-        <v>5.205744504928589</v>
+        <v>4.838683843612671</v>
       </c>
       <c r="J27" t="n">
-        <v>5.39622974395752</v>
+        <v>4.451984167098999</v>
       </c>
       <c r="K27" t="n">
-        <v>5.030173778533936</v>
+        <v>4.889592409133911</v>
       </c>
       <c r="L27" t="n">
-        <v>5.180701756477356</v>
+        <v>4.779348969459534</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.505014419555664</v>
+        <v>4.563411951065063</v>
       </c>
       <c r="C28" t="n">
-        <v>4.035232782363892</v>
+        <v>4.297575235366821</v>
       </c>
       <c r="D28" t="n">
-        <v>4.527957677841187</v>
+        <v>4.567886829376221</v>
       </c>
       <c r="E28" t="n">
-        <v>4.605256795883179</v>
+        <v>4.681631326675415</v>
       </c>
       <c r="F28" t="n">
-        <v>4.358391761779785</v>
+        <v>3.981870174407959</v>
       </c>
       <c r="G28" t="n">
-        <v>4.23619556427002</v>
+        <v>4.082544326782227</v>
       </c>
       <c r="H28" t="n">
-        <v>4.279589891433716</v>
+        <v>4.186850309371948</v>
       </c>
       <c r="I28" t="n">
-        <v>4.414752244949341</v>
+        <v>4.3284912109375</v>
       </c>
       <c r="J28" t="n">
-        <v>4.347923040390015</v>
+        <v>4.10652756690979</v>
       </c>
       <c r="K28" t="n">
-        <v>4.29604172706604</v>
+        <v>3.948752403259277</v>
       </c>
       <c r="L28" t="n">
-        <v>4.360635590553284</v>
+        <v>4.274554133415222</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.19230580329895</v>
+        <v>5.075402736663818</v>
       </c>
       <c r="C29" t="n">
-        <v>4.970339059829712</v>
+        <v>6.453332424163818</v>
       </c>
       <c r="D29" t="n">
-        <v>4.430700540542603</v>
+        <v>5.800693988800049</v>
       </c>
       <c r="E29" t="n">
-        <v>4.032150030136108</v>
+        <v>4.772148847579956</v>
       </c>
       <c r="F29" t="n">
-        <v>4.148216485977173</v>
+        <v>5.118863344192505</v>
       </c>
       <c r="G29" t="n">
-        <v>4.46736478805542</v>
+        <v>5.026960849761963</v>
       </c>
       <c r="H29" t="n">
-        <v>4.683091878890991</v>
+        <v>4.842463254928589</v>
       </c>
       <c r="I29" t="n">
-        <v>4.863850831985474</v>
+        <v>5.093330860137939</v>
       </c>
       <c r="J29" t="n">
-        <v>4.559619665145874</v>
+        <v>6.289364576339722</v>
       </c>
       <c r="K29" t="n">
-        <v>4.186102628707886</v>
+        <v>6.007408618927002</v>
       </c>
       <c r="L29" t="n">
-        <v>4.453374171257019</v>
+        <v>5.447996950149536</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.212058067321777</v>
+        <v>4.021595239639282</v>
       </c>
       <c r="C30" t="n">
-        <v>4.763110876083374</v>
+        <v>3.927294015884399</v>
       </c>
       <c r="D30" t="n">
-        <v>4.236610651016235</v>
+        <v>4.008569478988647</v>
       </c>
       <c r="E30" t="n">
-        <v>4.600209474563599</v>
+        <v>3.859177112579346</v>
       </c>
       <c r="F30" t="n">
-        <v>4.814720630645752</v>
+        <v>4.310068130493164</v>
       </c>
       <c r="G30" t="n">
-        <v>4.638181209564209</v>
+        <v>4.107074737548828</v>
       </c>
       <c r="H30" t="n">
-        <v>4.766327142715454</v>
+        <v>4.292826175689697</v>
       </c>
       <c r="I30" t="n">
-        <v>4.700514078140259</v>
+        <v>4.034020662307739</v>
       </c>
       <c r="J30" t="n">
-        <v>4.191325187683105</v>
+        <v>5.85696005821228</v>
       </c>
       <c r="K30" t="n">
-        <v>4.940921783447266</v>
+        <v>4.776629447937012</v>
       </c>
       <c r="L30" t="n">
-        <v>4.586397910118103</v>
+        <v>4.319421505928039</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>3.897554159164429</v>
+        <v>3.928315877914429</v>
       </c>
       <c r="C31" t="n">
-        <v>4.26066255569458</v>
+        <v>4.68537974357605</v>
       </c>
       <c r="D31" t="n">
-        <v>3.832227468490601</v>
+        <v>4.094413757324219</v>
       </c>
       <c r="E31" t="n">
-        <v>3.829246759414673</v>
+        <v>4.192121028900146</v>
       </c>
       <c r="F31" t="n">
-        <v>4.115033388137817</v>
+        <v>4.363707065582275</v>
       </c>
       <c r="G31" t="n">
-        <v>3.997838735580444</v>
+        <v>3.770515918731689</v>
       </c>
       <c r="H31" t="n">
-        <v>3.847692728042603</v>
+        <v>4.231742143630981</v>
       </c>
       <c r="I31" t="n">
-        <v>3.859151601791382</v>
+        <v>3.947796106338501</v>
       </c>
       <c r="J31" t="n">
-        <v>3.994841575622559</v>
+        <v>4.419800996780396</v>
       </c>
       <c r="K31" t="n">
-        <v>3.859171628952026</v>
+        <v>5.640968561172485</v>
       </c>
       <c r="L31" t="n">
-        <v>3.949342060089111</v>
+        <v>4.327476119995117</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.325972080230713</v>
+        <v>4.889623403549194</v>
       </c>
       <c r="C32" t="n">
-        <v>3.989313364028931</v>
+        <v>4.346956014633179</v>
       </c>
       <c r="D32" t="n">
-        <v>5.119961500167847</v>
+        <v>3.923540592193604</v>
       </c>
       <c r="E32" t="n">
-        <v>4.652141094207764</v>
+        <v>4.385956048965454</v>
       </c>
       <c r="F32" t="n">
-        <v>4.081103324890137</v>
+        <v>4.420769929885864</v>
       </c>
       <c r="G32" t="n">
-        <v>4.138946533203125</v>
+        <v>4.566950559616089</v>
       </c>
       <c r="H32" t="n">
-        <v>4.542575836181641</v>
+        <v>4.028277158737183</v>
       </c>
       <c r="I32" t="n">
-        <v>4.381844043731689</v>
+        <v>4.065666913986206</v>
       </c>
       <c r="J32" t="n">
-        <v>3.91352653503418</v>
+        <v>3.99884819984436</v>
       </c>
       <c r="K32" t="n">
-        <v>4.170401573181152</v>
+        <v>4.749439477920532</v>
       </c>
       <c r="L32" t="n">
-        <v>4.331578588485717</v>
+        <v>4.337602829933166</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.28058648109436</v>
+        <v>4.832573652267456</v>
       </c>
       <c r="C33" t="n">
-        <v>4.958863496780396</v>
+        <v>5.420705795288086</v>
       </c>
       <c r="D33" t="n">
-        <v>4.437690496444702</v>
+        <v>4.629977226257324</v>
       </c>
       <c r="E33" t="n">
-        <v>4.85014533996582</v>
+        <v>4.717269659042358</v>
       </c>
       <c r="F33" t="n">
-        <v>4.451632022857666</v>
+        <v>4.389599323272705</v>
       </c>
       <c r="G33" t="n">
-        <v>4.522975206375122</v>
+        <v>4.710287570953369</v>
       </c>
       <c r="H33" t="n">
-        <v>4.609659671783447</v>
+        <v>4.676841020584106</v>
       </c>
       <c r="I33" t="n">
-        <v>5.215723752975464</v>
+        <v>4.509770393371582</v>
       </c>
       <c r="J33" t="n">
-        <v>4.280596494674683</v>
+        <v>5.900296926498413</v>
       </c>
       <c r="K33" t="n">
-        <v>4.609240293502808</v>
+        <v>4.801548480987549</v>
       </c>
       <c r="L33" t="n">
-        <v>4.621711325645447</v>
+        <v>4.858887004852295</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>4.053680658340454</v>
+        <v>3.692926168441772</v>
       </c>
       <c r="C34" t="n">
-        <v>3.672148466110229</v>
+        <v>4.31929087638855</v>
       </c>
       <c r="D34" t="n">
-        <v>4.479169368743896</v>
+        <v>5.672111749649048</v>
       </c>
       <c r="E34" t="n">
-        <v>4.680136919021606</v>
+        <v>4.297508001327515</v>
       </c>
       <c r="F34" t="n">
-        <v>4.160407304763794</v>
+        <v>4.037769079208374</v>
       </c>
       <c r="G34" t="n">
-        <v>3.631758213043213</v>
+        <v>4.160476207733154</v>
       </c>
       <c r="H34" t="n">
-        <v>3.828264713287354</v>
+        <v>4.180399417877197</v>
       </c>
       <c r="I34" t="n">
-        <v>3.918527603149414</v>
+        <v>4.271283864974976</v>
       </c>
       <c r="J34" t="n">
-        <v>3.58635687828064</v>
+        <v>4.434276819229126</v>
       </c>
       <c r="K34" t="n">
-        <v>3.686099290847778</v>
+        <v>3.847219228744507</v>
       </c>
       <c r="L34" t="n">
-        <v>3.969654941558838</v>
+        <v>4.291326141357422</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>5.782660484313965</v>
+        <v>5.131357192993164</v>
       </c>
       <c r="C35" t="n">
-        <v>5.75352144241333</v>
+        <v>5.693046092987061</v>
       </c>
       <c r="D35" t="n">
-        <v>5.314693689346313</v>
+        <v>5.047327756881714</v>
       </c>
       <c r="E35" t="n">
-        <v>5.294709920883179</v>
+        <v>4.981331586837769</v>
       </c>
       <c r="F35" t="n">
-        <v>5.463305950164795</v>
+        <v>4.8558030128479</v>
       </c>
       <c r="G35" t="n">
-        <v>4.967584848403931</v>
+        <v>4.749494791030884</v>
       </c>
       <c r="H35" t="n">
-        <v>5.430874824523926</v>
+        <v>5.002011299133301</v>
       </c>
       <c r="I35" t="n">
-        <v>4.750621318817139</v>
+        <v>4.57427716255188</v>
       </c>
       <c r="J35" t="n">
-        <v>5.334606170654297</v>
+        <v>4.761658906936646</v>
       </c>
       <c r="K35" t="n">
-        <v>5.041887283325195</v>
+        <v>4.565148591995239</v>
       </c>
       <c r="L35" t="n">
-        <v>5.313446593284607</v>
+        <v>4.936145639419555</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.672940731048584</v>
+        <v>3.78768253326416</v>
       </c>
       <c r="C36" t="n">
-        <v>3.86942195892334</v>
+        <v>3.88946795463562</v>
       </c>
       <c r="D36" t="n">
-        <v>3.682434558868408</v>
+        <v>3.301921606063843</v>
       </c>
       <c r="E36" t="n">
-        <v>3.538789987564087</v>
+        <v>3.45500111579895</v>
       </c>
       <c r="F36" t="n">
-        <v>3.518357038497925</v>
+        <v>3.483137130737305</v>
       </c>
       <c r="G36" t="n">
-        <v>3.427087306976318</v>
+        <v>3.340579986572266</v>
       </c>
       <c r="H36" t="n">
-        <v>3.504378795623779</v>
+        <v>3.552457809448242</v>
       </c>
       <c r="I36" t="n">
-        <v>3.660006761550903</v>
+        <v>3.41631031036377</v>
       </c>
       <c r="J36" t="n">
-        <v>3.466969728469849</v>
+        <v>3.823847055435181</v>
       </c>
       <c r="K36" t="n">
-        <v>3.910342216491699</v>
+        <v>4.16184139251709</v>
       </c>
       <c r="L36" t="n">
-        <v>3.625072908401489</v>
+        <v>3.621224689483642</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.357661962509155</v>
+        <v>4.815521001815796</v>
       </c>
       <c r="C37" t="n">
-        <v>4.771473169326782</v>
+        <v>4.617580413818359</v>
       </c>
       <c r="D37" t="n">
-        <v>4.504007577896118</v>
+        <v>4.333770036697388</v>
       </c>
       <c r="E37" t="n">
-        <v>4.688545227050781</v>
+        <v>4.194595575332642</v>
       </c>
       <c r="F37" t="n">
-        <v>4.58530592918396</v>
+        <v>4.413312673568726</v>
       </c>
       <c r="G37" t="n">
-        <v>4.404762029647827</v>
+        <v>4.793245077133179</v>
       </c>
       <c r="H37" t="n">
-        <v>4.374352216720581</v>
+        <v>4.836327314376831</v>
       </c>
       <c r="I37" t="n">
-        <v>5.164849042892456</v>
+        <v>4.377880096435547</v>
       </c>
       <c r="J37" t="n">
-        <v>4.598291397094727</v>
+        <v>4.266486406326294</v>
       </c>
       <c r="K37" t="n">
-        <v>4.606247663497925</v>
+        <v>4.068561553955078</v>
       </c>
       <c r="L37" t="n">
-        <v>4.605549621582031</v>
+        <v>4.471728014945984</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.834681272506714</v>
+        <v>4.479155540466309</v>
       </c>
       <c r="C38" t="n">
-        <v>4.284586906433105</v>
+        <v>4.279393196105957</v>
       </c>
       <c r="D38" t="n">
-        <v>4.303542852401733</v>
+        <v>4.718266725540161</v>
       </c>
       <c r="E38" t="n">
-        <v>4.483156204223633</v>
+        <v>4.504798412322998</v>
       </c>
       <c r="F38" t="n">
-        <v>4.895488977432251</v>
+        <v>5.080317497253418</v>
       </c>
       <c r="G38" t="n">
-        <v>5.082557201385498</v>
+        <v>4.617002248764038</v>
       </c>
       <c r="H38" t="n">
-        <v>4.718460321426392</v>
+        <v>4.29833459854126</v>
       </c>
       <c r="I38" t="n">
-        <v>5.002263069152832</v>
+        <v>4.470388650894165</v>
       </c>
       <c r="J38" t="n">
-        <v>4.537948131561279</v>
+        <v>4.297340631484985</v>
       </c>
       <c r="K38" t="n">
-        <v>4.913982391357422</v>
+        <v>5.198619842529297</v>
       </c>
       <c r="L38" t="n">
-        <v>4.705666732788086</v>
+        <v>4.594361734390259</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.167393207550049</v>
+        <v>3.945465087890625</v>
       </c>
       <c r="C39" t="n">
-        <v>3.906540155410767</v>
+        <v>3.661173582077026</v>
       </c>
       <c r="D39" t="n">
-        <v>3.816267251968384</v>
+        <v>3.702096223831177</v>
       </c>
       <c r="E39" t="n">
-        <v>4.33045506477356</v>
+        <v>3.792347192764282</v>
       </c>
       <c r="F39" t="n">
-        <v>4.15542197227478</v>
+        <v>4.174089670181274</v>
       </c>
       <c r="G39" t="n">
-        <v>3.676690340042114</v>
+        <v>4.304334163665771</v>
       </c>
       <c r="H39" t="n">
-        <v>4.206326961517334</v>
+        <v>8.459519147872925</v>
       </c>
       <c r="I39" t="n">
-        <v>4.50704288482666</v>
+        <v>5.501575469970703</v>
       </c>
       <c r="J39" t="n">
-        <v>3.927002429962158</v>
+        <v>4.56250786781311</v>
       </c>
       <c r="K39" t="n">
-        <v>4.139935731887817</v>
+        <v>3.903178930282593</v>
       </c>
       <c r="L39" t="n">
-        <v>4.083307600021362</v>
+        <v>4.600628733634949</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.783808469772339</v>
+        <v>4.456189393997192</v>
       </c>
       <c r="C40" t="n">
-        <v>4.69202709197998</v>
+        <v>4.640527009963989</v>
       </c>
       <c r="D40" t="n">
-        <v>5.238149404525757</v>
+        <v>4.639233827590942</v>
       </c>
       <c r="E40" t="n">
-        <v>4.262131929397583</v>
+        <v>4.535468101501465</v>
       </c>
       <c r="F40" t="n">
-        <v>4.2706458568573</v>
+        <v>4.298591613769531</v>
       </c>
       <c r="G40" t="n">
-        <v>4.534935712814331</v>
+        <v>5.494025230407715</v>
       </c>
       <c r="H40" t="n">
-        <v>4.858605146408081</v>
+        <v>4.61824893951416</v>
       </c>
       <c r="I40" t="n">
-        <v>4.608268976211548</v>
+        <v>4.502052307128906</v>
       </c>
       <c r="J40" t="n">
-        <v>4.702427625656128</v>
+        <v>5.061627626419067</v>
       </c>
       <c r="K40" t="n">
-        <v>4.665355682373047</v>
+        <v>4.339513778686523</v>
       </c>
       <c r="L40" t="n">
-        <v>4.66163558959961</v>
+        <v>4.65854778289795</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.49878716468811</v>
+        <v>4.114571094512939</v>
       </c>
       <c r="C41" t="n">
-        <v>4.281343698501587</v>
+        <v>5.055739641189575</v>
       </c>
       <c r="D41" t="n">
-        <v>4.585556268692017</v>
+        <v>4.490517139434814</v>
       </c>
       <c r="E41" t="n">
-        <v>4.366637229919434</v>
+        <v>4.513430118560791</v>
       </c>
       <c r="F41" t="n">
-        <v>4.56514573097229</v>
+        <v>4.454227447509766</v>
       </c>
       <c r="G41" t="n">
-        <v>4.507761716842651</v>
+        <v>4.47969126701355</v>
       </c>
       <c r="H41" t="n">
-        <v>4.447424411773682</v>
+        <v>4.253718137741089</v>
       </c>
       <c r="I41" t="n">
-        <v>4.210068702697754</v>
+        <v>4.606299161911011</v>
       </c>
       <c r="J41" t="n">
-        <v>4.508749961853027</v>
+        <v>4.412797927856445</v>
       </c>
       <c r="K41" t="n">
-        <v>4.402536869049072</v>
+        <v>4.1607346534729</v>
       </c>
       <c r="L41" t="n">
-        <v>4.437401175498962</v>
+        <v>4.454172658920288</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.158064842224121</v>
+        <v>4.990665197372437</v>
       </c>
       <c r="C42" t="n">
-        <v>4.657386541366577</v>
+        <v>4.555240631103516</v>
       </c>
       <c r="D42" t="n">
-        <v>4.419490575790405</v>
+        <v>4.376184225082397</v>
       </c>
       <c r="E42" t="n">
-        <v>4.872332811355591</v>
+        <v>4.240544080734253</v>
       </c>
       <c r="F42" t="n">
-        <v>4.825946569442749</v>
+        <v>4.376642227172852</v>
       </c>
       <c r="G42" t="n">
-        <v>4.531686067581177</v>
+        <v>4.114819049835205</v>
       </c>
       <c r="H42" t="n">
-        <v>4.507789611816406</v>
+        <v>4.848839521408081</v>
       </c>
       <c r="I42" t="n">
-        <v>4.512766122817993</v>
+        <v>4.632719039916992</v>
       </c>
       <c r="J42" t="n">
-        <v>4.625959873199463</v>
+        <v>4.365092277526855</v>
       </c>
       <c r="K42" t="n">
-        <v>4.5910484790802</v>
+        <v>4.375922918319702</v>
       </c>
       <c r="L42" t="n">
-        <v>4.670247149467468</v>
+        <v>4.487666916847229</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.618021011352539</v>
+        <v>4.74595832824707</v>
       </c>
       <c r="C43" t="n">
-        <v>4.349169492721558</v>
+        <v>4.657429218292236</v>
       </c>
       <c r="D43" t="n">
-        <v>4.47684121131897</v>
+        <v>4.702287673950195</v>
       </c>
       <c r="E43" t="n">
-        <v>4.906718015670776</v>
+        <v>4.897814273834229</v>
       </c>
       <c r="F43" t="n">
-        <v>4.28864049911499</v>
+        <v>5.117242097854614</v>
       </c>
       <c r="G43" t="n">
-        <v>5.205745458602905</v>
+        <v>4.601053714752197</v>
       </c>
       <c r="H43" t="n">
-        <v>5.151372671127319</v>
+        <v>4.958635330200195</v>
       </c>
       <c r="I43" t="n">
-        <v>4.513989925384521</v>
+        <v>4.369645595550537</v>
       </c>
       <c r="J43" t="n">
-        <v>5.208729028701782</v>
+        <v>4.609029293060303</v>
       </c>
       <c r="K43" t="n">
-        <v>4.851635932922363</v>
+        <v>4.937660217285156</v>
       </c>
       <c r="L43" t="n">
-        <v>4.757086324691772</v>
+        <v>4.759675574302674</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.100042819976807</v>
+        <v>3.860471248626709</v>
       </c>
       <c r="C44" t="n">
-        <v>3.926482439041138</v>
+        <v>4.310323238372803</v>
       </c>
       <c r="D44" t="n">
-        <v>4.168857336044312</v>
+        <v>4.585768222808838</v>
       </c>
       <c r="E44" t="n">
-        <v>5.231190204620361</v>
+        <v>4.125786542892456</v>
       </c>
       <c r="F44" t="n">
-        <v>4.119992971420288</v>
+        <v>3.860960006713867</v>
       </c>
       <c r="G44" t="n">
-        <v>4.598258972167969</v>
+        <v>4.282410621643066</v>
       </c>
       <c r="H44" t="n">
-        <v>3.973380088806152</v>
+        <v>3.883658409118652</v>
       </c>
       <c r="I44" t="n">
-        <v>4.588312387466431</v>
+        <v>4.105138301849365</v>
       </c>
       <c r="J44" t="n">
-        <v>4.455636024475098</v>
+        <v>4.593832492828369</v>
       </c>
       <c r="K44" t="n">
-        <v>4.511286020278931</v>
+        <v>4.267186641693115</v>
       </c>
       <c r="L44" t="n">
-        <v>4.367343926429749</v>
+        <v>4.187553572654724</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.576337337493896</v>
+        <v>3.951972961425781</v>
       </c>
       <c r="C45" t="n">
-        <v>4.177348375320435</v>
+        <v>4.59487771987915</v>
       </c>
       <c r="D45" t="n">
-        <v>4.510996341705322</v>
+        <v>4.038290739059448</v>
       </c>
       <c r="E45" t="n">
-        <v>4.383844375610352</v>
+        <v>4.280127763748169</v>
       </c>
       <c r="F45" t="n">
-        <v>4.654132127761841</v>
+        <v>4.121551513671875</v>
       </c>
       <c r="G45" t="n">
-        <v>4.271623849868774</v>
+        <v>3.950442790985107</v>
       </c>
       <c r="H45" t="n">
-        <v>4.512993574142456</v>
+        <v>4.39189338684082</v>
       </c>
       <c r="I45" t="n">
-        <v>4.216244220733643</v>
+        <v>4.035750150680542</v>
       </c>
       <c r="J45" t="n">
-        <v>3.945433616638184</v>
+        <v>3.848208427429199</v>
       </c>
       <c r="K45" t="n">
-        <v>3.947426557540894</v>
+        <v>4.022290229797363</v>
       </c>
       <c r="L45" t="n">
-        <v>4.31963803768158</v>
+        <v>4.123540568351745</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.46560263633728</v>
+        <v>4.189829111099243</v>
       </c>
       <c r="C46" t="n">
-        <v>4.320484638214111</v>
+        <v>4.486097812652588</v>
       </c>
       <c r="D46" t="n">
-        <v>4.499026536941528</v>
+        <v>4.142354011535645</v>
       </c>
       <c r="E46" t="n">
-        <v>4.810762166976929</v>
+        <v>4.033112049102783</v>
       </c>
       <c r="F46" t="n">
-        <v>4.775820255279541</v>
+        <v>4.390603303909302</v>
       </c>
       <c r="G46" t="n">
-        <v>4.991276741027832</v>
+        <v>4.418517112731934</v>
       </c>
       <c r="H46" t="n">
-        <v>5.200223207473755</v>
+        <v>4.35290002822876</v>
       </c>
       <c r="I46" t="n">
-        <v>4.986298561096191</v>
+        <v>4.36591649055481</v>
       </c>
       <c r="J46" t="n">
-        <v>4.3758385181427</v>
+        <v>4.396819829940796</v>
       </c>
       <c r="K46" t="n">
-        <v>5.117484569549561</v>
+        <v>4.771442651748657</v>
       </c>
       <c r="L46" t="n">
-        <v>4.754281783103943</v>
+        <v>4.354759240150452</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.517989873886108</v>
+        <v>4.707555532455444</v>
       </c>
       <c r="C47" t="n">
-        <v>5.233678817749023</v>
+        <v>4.553273916244507</v>
       </c>
       <c r="D47" t="n">
-        <v>4.027728319168091</v>
+        <v>4.360167503356934</v>
       </c>
       <c r="E47" t="n">
-        <v>4.852153062820435</v>
+        <v>4.455826759338379</v>
       </c>
       <c r="F47" t="n">
-        <v>4.393806219100952</v>
+        <v>4.371389150619507</v>
       </c>
       <c r="G47" t="n">
-        <v>4.714495182037354</v>
+        <v>4.216264963150024</v>
       </c>
       <c r="H47" t="n">
-        <v>4.817097425460815</v>
+        <v>6.132562160491943</v>
       </c>
       <c r="I47" t="n">
-        <v>4.853363275527954</v>
+        <v>4.529494762420654</v>
       </c>
       <c r="J47" t="n">
-        <v>5.190486907958984</v>
+        <v>4.975629568099976</v>
       </c>
       <c r="K47" t="n">
-        <v>4.262408494949341</v>
+        <v>4.848902225494385</v>
       </c>
       <c r="L47" t="n">
-        <v>4.686320757865905</v>
+        <v>4.715106654167175</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.30832052230835</v>
+        <v>4.638993740081787</v>
       </c>
       <c r="C48" t="n">
-        <v>4.746146678924561</v>
+        <v>4.324286937713623</v>
       </c>
       <c r="D48" t="n">
-        <v>4.764115810394287</v>
+        <v>4.539382934570312</v>
       </c>
       <c r="E48" t="n">
-        <v>4.993998050689697</v>
+        <v>4.344226598739624</v>
       </c>
       <c r="F48" t="n">
-        <v>4.803494453430176</v>
+        <v>5.338669300079346</v>
       </c>
       <c r="G48" t="n">
-        <v>4.318275690078735</v>
+        <v>4.111804246902466</v>
       </c>
       <c r="H48" t="n">
-        <v>4.641424655914307</v>
+        <v>4.286375999450684</v>
       </c>
       <c r="I48" t="n">
-        <v>4.969588041305542</v>
+        <v>4.501799821853638</v>
       </c>
       <c r="J48" t="n">
-        <v>4.895799398422241</v>
+        <v>4.583103895187378</v>
       </c>
       <c r="K48" t="n">
-        <v>4.422543525695801</v>
+        <v>4.311833143234253</v>
       </c>
       <c r="L48" t="n">
-        <v>4.68637068271637</v>
+        <v>4.498047661781311</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>5.855281114578247</v>
+        <v>4.707571029663086</v>
       </c>
       <c r="C49" t="n">
-        <v>4.753139019012451</v>
+        <v>4.705533981323242</v>
       </c>
       <c r="D49" t="n">
-        <v>4.922687292098999</v>
+        <v>4.956877708435059</v>
       </c>
       <c r="E49" t="n">
-        <v>4.908705711364746</v>
+        <v>4.661683320999146</v>
       </c>
       <c r="F49" t="n">
-        <v>5.021929264068604</v>
+        <v>4.472621202468872</v>
       </c>
       <c r="G49" t="n">
-        <v>4.426062107086182</v>
+        <v>4.494082450866699</v>
       </c>
       <c r="H49" t="n">
-        <v>4.572596788406372</v>
+        <v>4.717535495758057</v>
       </c>
       <c r="I49" t="n">
-        <v>4.666356801986694</v>
+        <v>4.445284843444824</v>
       </c>
       <c r="J49" t="n">
-        <v>5.026899576187134</v>
+        <v>4.898409366607666</v>
       </c>
       <c r="K49" t="n">
-        <v>4.713219404220581</v>
+        <v>4.714910745620728</v>
       </c>
       <c r="L49" t="n">
-        <v>4.886687707901001</v>
+        <v>4.677451014518738</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.872440338134766</v>
+        <v>3.662477970123291</v>
       </c>
       <c r="C50" t="n">
-        <v>3.985625267028809</v>
+        <v>3.568758487701416</v>
       </c>
       <c r="D50" t="n">
-        <v>3.460287809371948</v>
+        <v>3.535340785980225</v>
       </c>
       <c r="E50" t="n">
-        <v>3.49740743637085</v>
+        <v>3.696377515792847</v>
       </c>
       <c r="F50" t="n">
-        <v>3.611593008041382</v>
+        <v>3.47684645652771</v>
       </c>
       <c r="G50" t="n">
-        <v>3.495425701141357</v>
+        <v>3.828260183334351</v>
       </c>
       <c r="H50" t="n">
-        <v>3.50637674331665</v>
+        <v>3.647758722305298</v>
       </c>
       <c r="I50" t="n">
-        <v>3.655508518218994</v>
+        <v>3.482641935348511</v>
       </c>
       <c r="J50" t="n">
-        <v>3.470478057861328</v>
+        <v>3.497596025466919</v>
       </c>
       <c r="K50" t="n">
-        <v>3.556232452392578</v>
+        <v>3.472153186798096</v>
       </c>
       <c r="L50" t="n">
-        <v>3.611137533187866</v>
+        <v>3.586821126937866</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.047460556030273</v>
+        <v>4.495064258575439</v>
       </c>
       <c r="C51" t="n">
-        <v>4.674322843551636</v>
+        <v>4.484105348587036</v>
       </c>
       <c r="D51" t="n">
-        <v>4.171630859375</v>
+        <v>4.633933305740356</v>
       </c>
       <c r="E51" t="n">
-        <v>4.459896326065063</v>
+        <v>4.322286367416382</v>
       </c>
       <c r="F51" t="n">
-        <v>4.03748607635498</v>
+        <v>4.642089605331421</v>
       </c>
       <c r="G51" t="n">
-        <v>4.109820127487183</v>
+        <v>4.45964789390564</v>
       </c>
       <c r="H51" t="n">
-        <v>4.396581888198853</v>
+        <v>4.21335768699646</v>
       </c>
       <c r="I51" t="n">
-        <v>4.182129144668579</v>
+        <v>4.435158729553223</v>
       </c>
       <c r="J51" t="n">
-        <v>4.315264940261841</v>
+        <v>4.630215644836426</v>
       </c>
       <c r="K51" t="n">
-        <v>4.202059030532837</v>
+        <v>4.042708873748779</v>
       </c>
       <c r="L51" t="n">
-        <v>4.259665179252624</v>
+        <v>4.435856771469116</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.448039407730103</v>
+        <v>4.448022060394287</v>
       </c>
       <c r="C52" t="n">
-        <v>4.520993180274964</v>
+        <v>4.549065179824829</v>
       </c>
       <c r="D52" t="n">
-        <v>4.509196634292603</v>
+        <v>4.398020806312561</v>
       </c>
       <c r="E52" t="n">
-        <v>4.51638922214508</v>
+        <v>4.402209620475769</v>
       </c>
       <c r="F52" t="n">
-        <v>4.510547080039978</v>
+        <v>4.428386564254761</v>
       </c>
       <c r="G52" t="n">
-        <v>4.457135634422302</v>
+        <v>4.430651807785035</v>
       </c>
       <c r="H52" t="n">
-        <v>4.487902340888977</v>
+        <v>4.531475725173951</v>
       </c>
       <c r="I52" t="n">
-        <v>4.536457056999207</v>
+        <v>4.377578859329224</v>
       </c>
       <c r="J52" t="n">
-        <v>4.595701155662536</v>
+        <v>4.570833907127381</v>
       </c>
       <c r="K52" t="n">
-        <v>4.471560878753662</v>
+        <v>4.460759491920471</v>
       </c>
       <c r="L52" t="n">
-        <v>4.505392259120941</v>
+        <v>4.459700402259826</v>
       </c>
     </row>
   </sheetData>
